--- a/worlds/spyro_aht/setup/Gem Research.xlsx
+++ b/worlds/spyro_aht/setup/Gem Research.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sean\Downloads\Archipelago Stuff\apworlds\PhoenixAP\worlds\spyro_aht\setup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD8F4A0C-EC1E-4D09-8506-301519FAFF40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59D95D44-01AB-4806-9A15-D0C2C463CF32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="697" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2042,9 +2042,6 @@
     <t>armored chests by dragon egg via cannon/and baskets by dragon egg</t>
   </si>
   <si>
-    <t>on the ground/meatl chests/headbash chests</t>
-  </si>
-  <si>
     <t>on the ground/baskets/and metal chests after electric platform</t>
   </si>
   <si>
@@ -2349,6 +2346,9 @@
   </si>
   <si>
     <t>horn diveable barrels/crates</t>
+  </si>
+  <si>
+    <t>on the ground/metal chests/headbash chests</t>
   </si>
 </sst>
 </file>
@@ -2927,7 +2927,7 @@
         <v>395</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>20</v>
@@ -2941,7 +2941,7 @@
         <v>360</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>20</v>
@@ -3941,7 +3941,7 @@
         <v>1003</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>20</v>
@@ -3955,7 +3955,7 @@
         <v>928</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>20</v>
@@ -4436,7 +4436,7 @@
         <v>675</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D123" s="3" t="s">
         <v>20</v>
@@ -4450,7 +4450,7 @@
         <v>700</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D124" s="3" t="s">
         <v>20</v>
@@ -5834,7 +5834,7 @@
         <v>755</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D223" s="3" t="s">
         <v>20</v>
@@ -5848,7 +5848,7 @@
         <v>1435</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D224" s="3" t="s">
         <v>20</v>
@@ -6651,7 +6651,7 @@
         <v>200</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D282" s="3" t="s">
         <v>20</v>
@@ -6665,7 +6665,7 @@
         <v>200</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D283" s="3" t="s">
         <v>20</v>
@@ -7272,7 +7272,7 @@
         <v>900</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D327" s="3" t="s">
         <v>20</v>
@@ -7286,7 +7286,7 @@
         <v>800</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D328" s="3" t="s">
         <v>20</v>
@@ -7721,7 +7721,7 @@
         <v>50</v>
       </c>
       <c r="C359" s="1" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D359" s="3" t="s">
         <v>35</v>
@@ -8132,7 +8132,7 @@
         <v>1906</v>
       </c>
       <c r="C389" s="1" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D389" s="3" t="s">
         <v>20</v>
@@ -8146,7 +8146,7 @@
         <v>1956</v>
       </c>
       <c r="C390" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D390" s="3" t="s">
         <v>20</v>
@@ -8219,7 +8219,7 @@
         <v>50</v>
       </c>
       <c r="C395" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D395" s="3" t="s">
         <v>214</v>
@@ -8905,7 +8905,7 @@
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A445" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B445" s="1">
         <v>110</v>
@@ -8919,7 +8919,7 @@
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A446" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B446" s="1">
         <v>156</v>
@@ -8936,7 +8936,7 @@
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A447" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B447" s="1">
         <v>400</v>
@@ -8950,7 +8950,7 @@
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A448" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B448" s="1">
         <v>500</v>
@@ -8964,7 +8964,7 @@
     </row>
     <row r="449" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A449" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B449" s="1">
         <v>400</v>
@@ -8978,7 +8978,7 @@
     </row>
     <row r="450" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A450" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B450" s="1">
         <v>60</v>
@@ -8992,7 +8992,7 @@
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A451" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B451" s="1">
         <v>100</v>
@@ -9006,7 +9006,7 @@
     </row>
     <row r="452" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A452" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B452" s="1">
         <v>1000</v>
@@ -9020,7 +9020,7 @@
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A453" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B453" s="1">
         <v>450</v>
@@ -9034,7 +9034,7 @@
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A454" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B454" s="1">
         <v>50</v>
@@ -9048,13 +9048,13 @@
     </row>
     <row r="455" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A455" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B455" s="1">
         <v>950</v>
       </c>
       <c r="C455" s="1" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D455" s="3" t="s">
         <v>20</v>
@@ -9062,13 +9062,13 @@
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A456" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B456" s="1">
         <v>900</v>
       </c>
       <c r="C456" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D456" s="3" t="s">
         <v>20</v>
@@ -9076,7 +9076,7 @@
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A457" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B457" s="1">
         <v>200</v>
@@ -9703,7 +9703,7 @@
         <v>800</v>
       </c>
       <c r="C502" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D502" s="3" t="s">
         <v>20</v>
@@ -9717,7 +9717,7 @@
         <v>830</v>
       </c>
       <c r="C503" s="1" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D503" s="3" t="s">
         <v>20</v>
@@ -10383,7 +10383,7 @@
         <v>270</v>
       </c>
       <c r="C551" s="1" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="D551" s="3" t="s">
         <v>20</v>
@@ -10808,7 +10808,7 @@
         <v>443</v>
       </c>
       <c r="C582" s="1" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D582" s="3" t="s">
         <v>20</v>
@@ -10822,7 +10822,7 @@
         <v>443</v>
       </c>
       <c r="C583" s="1" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D583" s="3" t="s">
         <v>20</v>
@@ -10836,7 +10836,7 @@
         <v>50</v>
       </c>
       <c r="C584" s="1" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D584" s="3" t="s">
         <v>20</v>
@@ -10928,13 +10928,13 @@
     </row>
     <row r="591" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A591" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B591" s="1">
         <v>50</v>
       </c>
       <c r="C591" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D591" s="3" t="s">
         <v>20</v>
@@ -10942,7 +10942,7 @@
     </row>
     <row r="592" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A592" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B592" s="1">
         <v>25</v>
@@ -10956,7 +10956,7 @@
     </row>
     <row r="593" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A593" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B593" s="1">
         <v>130</v>
@@ -10970,7 +10970,7 @@
     </row>
     <row r="594" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A594" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B594" s="1">
         <v>55</v>
@@ -10984,7 +10984,7 @@
     </row>
     <row r="595" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A595" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B595" s="1">
         <v>50</v>
@@ -12216,7 +12216,7 @@
         <v>1100</v>
       </c>
       <c r="C683" s="1" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="D683" s="3" t="s">
         <v>20</v>
@@ -12230,7 +12230,7 @@
         <v>900</v>
       </c>
       <c r="C684" s="1" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D684" s="3" t="s">
         <v>20</v>
@@ -12425,7 +12425,7 @@
     </row>
     <row r="699" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A699" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B699" s="1">
         <v>20</v>
@@ -12439,7 +12439,7 @@
     </row>
     <row r="700" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A700" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B700" s="1">
         <v>25</v>
@@ -12453,7 +12453,7 @@
     </row>
     <row r="701" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A701" s="1" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B701" s="1">
         <v>100</v>
@@ -12467,7 +12467,7 @@
     </row>
     <row r="702" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A702" s="1" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B702" s="1">
         <v>75</v>
@@ -12481,7 +12481,7 @@
     </row>
     <row r="703" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A703" s="1" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B703" s="1">
         <v>40</v>
@@ -12495,7 +12495,7 @@
     </row>
     <row r="704" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A704" s="1" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B704" s="1">
         <v>150</v>
@@ -12509,7 +12509,7 @@
     </row>
     <row r="705" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A705" s="1" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B705" s="1">
         <v>125</v>
@@ -12523,7 +12523,7 @@
     </row>
     <row r="706" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A706" s="1" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B706" s="1">
         <v>60</v>
@@ -12537,7 +12537,7 @@
     </row>
     <row r="707" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A707" s="1" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B707" s="1">
         <v>50</v>
@@ -12551,7 +12551,7 @@
     </row>
     <row r="708" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A708" s="1" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B708" s="1">
         <v>350</v>
@@ -12764,7 +12764,7 @@
     </row>
     <row r="723" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A723" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B723" s="1">
         <v>200</v>
@@ -12778,7 +12778,7 @@
     </row>
     <row r="724" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A724" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B724" s="1">
         <v>100</v>
@@ -12792,7 +12792,7 @@
     </row>
     <row r="725" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A725" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B725" s="1">
         <v>100</v>
@@ -12806,7 +12806,7 @@
     </row>
     <row r="726" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A726" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B726" s="1">
         <v>90</v>
@@ -12820,13 +12820,13 @@
     </row>
     <row r="727" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A727" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B727" s="1">
         <v>5240</v>
       </c>
       <c r="C727" s="1" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D727" s="3" t="s">
         <v>20</v>
@@ -12834,13 +12834,13 @@
     </row>
     <row r="728" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A728" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B728" s="1">
         <v>6980</v>
       </c>
       <c r="C728" s="1" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D728" s="3" t="s">
         <v>20</v>
@@ -12848,7 +12848,7 @@
     </row>
     <row r="729" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A729" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B729" s="1">
         <v>40</v>
@@ -12862,7 +12862,7 @@
     </row>
     <row r="730" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A730" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B730" s="1">
         <v>175</v>
@@ -12876,13 +12876,13 @@
     </row>
     <row r="731" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A731" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="B731" s="1">
+        <v>20</v>
+      </c>
+      <c r="C731" s="1" t="s">
         <v>667</v>
-      </c>
-      <c r="B731" s="1">
-        <v>20</v>
-      </c>
-      <c r="C731" s="1" t="s">
-        <v>668</v>
       </c>
       <c r="D731" s="3" t="s">
         <v>395</v>
@@ -12890,7 +12890,7 @@
     </row>
     <row r="732" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A732" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B732" s="1">
         <v>50</v>
@@ -13072,7 +13072,7 @@
     </row>
     <row r="745" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A745" s="1" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B745" s="1">
         <v>75</v>
@@ -13086,7 +13086,7 @@
     </row>
     <row r="746" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A746" s="1" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B746" s="1">
         <v>20</v>
@@ -13100,7 +13100,7 @@
     </row>
     <row r="747" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A747" s="1" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B747" s="1">
         <v>20</v>
@@ -13114,7 +13114,7 @@
     </row>
     <row r="748" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A748" s="1" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B748" s="1">
         <v>50</v>
@@ -13128,7 +13128,7 @@
     </row>
     <row r="749" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A749" s="1" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B749" s="1">
         <v>100</v>
@@ -13142,7 +13142,7 @@
     </row>
     <row r="750" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A750" s="1" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B750" s="1">
         <v>25</v>
@@ -14130,7 +14130,7 @@
     </row>
     <row r="823" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A823" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B823" s="1">
         <v>16353</v>
@@ -14138,7 +14138,7 @@
     </row>
     <row r="824" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A824" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B824" s="1">
         <f>B821-B822-B823</f>
@@ -14290,7 +14290,7 @@
         <v>395</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>20</v>
@@ -14304,7 +14304,7 @@
         <v>360</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>20</v>
@@ -15014,7 +15014,7 @@
         <v>1003</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>20</v>
@@ -15028,7 +15028,7 @@
         <v>928</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>20</v>
@@ -15372,7 +15372,7 @@
         <v>675</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>20</v>
@@ -15386,7 +15386,7 @@
         <v>700</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>20</v>
@@ -16123,7 +16123,7 @@
         <v>525</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>581</v>
+        <v>683</v>
       </c>
       <c r="D142" s="3" t="s">
         <v>20</v>
@@ -16193,7 +16193,7 @@
         <v>388</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D147" s="3" t="s">
         <v>220</v>
@@ -16264,7 +16264,7 @@
         <v>115</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D152" s="3" t="s">
         <v>48</v>
@@ -16362,7 +16362,7 @@
         <v>120</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D159" s="3" t="s">
         <v>48</v>
@@ -16390,7 +16390,7 @@
         <v>755</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D161" s="3" t="s">
         <v>20</v>
@@ -16404,7 +16404,7 @@
         <v>1435</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D162" s="3" t="s">
         <v>20</v>
@@ -16593,7 +16593,7 @@
         <v>180</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="D176" s="3" t="s">
         <v>20</v>
@@ -16776,7 +16776,7 @@
         <v>755</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D189" s="3" t="s">
         <v>20</v>
@@ -16861,7 +16861,7 @@
         <v>505</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D195" s="3" t="s">
         <v>20</v>
@@ -16889,7 +16889,7 @@
         <v>200</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D197" s="3" t="s">
         <v>20</v>
@@ -16903,7 +16903,7 @@
         <v>200</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D198" s="3" t="s">
         <v>20</v>
@@ -16932,7 +16932,7 @@
         <v>410</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D200" s="3" t="s">
         <v>20</v>
@@ -17008,7 +17008,7 @@
         <v>125</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D206" s="3" t="s">
         <v>48</v>
@@ -17121,7 +17121,7 @@
         <v>397</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D214" s="3" t="s">
         <v>66</v>
@@ -17387,7 +17387,7 @@
         <v>900</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D233" s="3" t="s">
         <v>20</v>
@@ -17401,7 +17401,7 @@
         <v>800</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D234" s="3" t="s">
         <v>20</v>
@@ -17529,7 +17529,7 @@
         <v>606</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D243" s="3" t="s">
         <v>20</v>
@@ -17557,7 +17557,7 @@
         <v>235</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D245" s="3" t="s">
         <v>20</v>
@@ -17572,7 +17572,7 @@
         <v>513</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D246" s="3" t="s">
         <v>20</v>
@@ -17670,7 +17670,7 @@
         <v>50</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D253" s="3" t="s">
         <v>35</v>
@@ -17713,7 +17713,7 @@
         <v>250</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D256" s="3" t="s">
         <v>20</v>
@@ -17728,7 +17728,7 @@
         <v>342</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D257" s="3" t="s">
         <v>20</v>
@@ -17775,7 +17775,7 @@
         <v>100</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D261" s="3" t="s">
         <v>20</v>
@@ -17873,7 +17873,7 @@
         <v>145</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D268" s="3" t="s">
         <v>48</v>
@@ -17902,7 +17902,7 @@
         <v>1016</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D270" s="3" t="s">
         <v>20</v>
@@ -17916,7 +17916,7 @@
         <v>1906</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D271" s="3" t="s">
         <v>20</v>
@@ -17930,7 +17930,7 @@
         <v>1956</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D272" s="3" t="s">
         <v>20</v>
@@ -17986,7 +17986,7 @@
         <v>50</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D276" s="3" t="s">
         <v>214</v>
@@ -18056,7 +18056,7 @@
         <v>141</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D281" s="3" t="s">
         <v>22</v>
@@ -18070,7 +18070,7 @@
         <v>571</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D282" s="3" t="s">
         <v>20</v>
@@ -18226,7 +18226,7 @@
         <v>1166</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D293" s="3" t="s">
         <v>20</v>
@@ -18464,7 +18464,7 @@
         <v>160</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D310" s="3" t="s">
         <v>297</v>
@@ -18491,7 +18491,7 @@
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A313" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B313" s="1">
         <v>110</v>
@@ -18505,13 +18505,13 @@
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A314" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B314" s="1">
         <v>656</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="D314" s="3" t="s">
         <v>20</v>
@@ -18519,7 +18519,7 @@
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A315" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B315" s="1">
         <v>1060</v>
@@ -18533,7 +18533,7 @@
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A316" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B316" s="1">
         <v>400</v>
@@ -18547,7 +18547,7 @@
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A317" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B317" s="1">
         <v>1000</v>
@@ -18561,13 +18561,13 @@
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A318" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B318" s="1">
         <v>200</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D318" s="3" t="s">
         <v>20</v>
@@ -18575,13 +18575,13 @@
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A319" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B319" s="1">
         <v>950</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D319" s="3" t="s">
         <v>20</v>
@@ -18589,13 +18589,13 @@
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A320" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B320" s="1">
         <v>900</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D320" s="3" t="s">
         <v>20</v>
@@ -18782,7 +18782,7 @@
         <v>40</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D334" s="3" t="s">
         <v>48</v>
@@ -18796,7 +18796,7 @@
         <v>175</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D335" s="3" t="s">
         <v>20</v>
@@ -18838,7 +18838,7 @@
         <v>39</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D338" s="3" t="s">
         <v>48</v>
@@ -18853,7 +18853,7 @@
         <v>475</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D339" s="3" t="s">
         <v>20</v>
@@ -18910,7 +18910,7 @@
         <v>208</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D343" s="3" t="s">
         <v>20</v>
@@ -19050,7 +19050,7 @@
         <v>140</v>
       </c>
       <c r="C353" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="D353" s="3" t="s">
         <v>48</v>
@@ -19064,7 +19064,7 @@
         <v>800</v>
       </c>
       <c r="C354" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D354" s="3" t="s">
         <v>20</v>
@@ -19078,7 +19078,7 @@
         <v>830</v>
       </c>
       <c r="C355" s="1" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D355" s="3" t="s">
         <v>20</v>
@@ -19106,7 +19106,7 @@
         <v>325</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D357" s="3" t="s">
         <v>20</v>
@@ -19274,7 +19274,7 @@
         <v>60</v>
       </c>
       <c r="C369" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D369" s="3" t="s">
         <v>20</v>
@@ -19358,7 +19358,7 @@
         <v>150</v>
       </c>
       <c r="C375" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D375" s="3" t="s">
         <v>20</v>
@@ -19373,7 +19373,7 @@
         <v>296</v>
       </c>
       <c r="C376" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D376" s="3" t="s">
         <v>20</v>
@@ -19387,7 +19387,7 @@
         <v>80</v>
       </c>
       <c r="C377" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D377" s="3" t="s">
         <v>22</v>
@@ -19588,7 +19588,7 @@
         <v>1684</v>
       </c>
       <c r="C392" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D392" s="3" t="s">
         <v>20</v>
@@ -19630,7 +19630,7 @@
         <v>40</v>
       </c>
       <c r="C395" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D395" s="3" t="s">
         <v>48</v>
@@ -19733,7 +19733,7 @@
         <v>572</v>
       </c>
       <c r="C403" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D403" s="3" t="s">
         <v>20</v>
@@ -19747,7 +19747,7 @@
         <v>161</v>
       </c>
       <c r="C404" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="D404" s="3" t="s">
         <v>20</v>
@@ -19761,7 +19761,7 @@
         <v>100</v>
       </c>
       <c r="C405" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D405" s="3" t="s">
         <v>388</v>
@@ -19887,7 +19887,7 @@
         <v>443</v>
       </c>
       <c r="C414" s="1" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D414" s="3" t="s">
         <v>20</v>
@@ -19901,7 +19901,7 @@
         <v>443</v>
       </c>
       <c r="C415" s="1" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D415" s="3" t="s">
         <v>20</v>
@@ -19915,7 +19915,7 @@
         <v>50</v>
       </c>
       <c r="C416" s="1" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D416" s="3" t="s">
         <v>20</v>
@@ -20007,7 +20007,7 @@
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A423" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B423" s="1">
         <v>50</v>
@@ -20021,7 +20021,7 @@
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A424" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B424" s="1">
         <v>25</v>
@@ -20035,14 +20035,14 @@
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A425" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B425" s="1">
         <f>130+55+50</f>
         <v>235</v>
       </c>
       <c r="C425" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D425" s="3" t="s">
         <v>20</v>
@@ -20154,7 +20154,7 @@
         <v>160</v>
       </c>
       <c r="C433" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D433" s="3" t="s">
         <v>20</v>
@@ -20169,7 +20169,7 @@
         <v>300</v>
       </c>
       <c r="C434" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D434" s="3" t="s">
         <v>388</v>
@@ -20240,7 +20240,7 @@
         <v>154</v>
       </c>
       <c r="C439" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D439" s="3" t="s">
         <v>20</v>
@@ -20268,7 +20268,7 @@
         <v>75</v>
       </c>
       <c r="C441" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="D441" s="3" t="s">
         <v>20</v>
@@ -20368,7 +20368,7 @@
         <v>658</v>
       </c>
       <c r="C448" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D448" s="3" t="s">
         <v>20</v>
@@ -21020,7 +21020,7 @@
         <v>1100</v>
       </c>
       <c r="C495" s="1" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="D495" s="3" t="s">
         <v>20</v>
@@ -21034,7 +21034,7 @@
         <v>900</v>
       </c>
       <c r="C496" s="1" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D496" s="3" t="s">
         <v>20</v>
@@ -21165,7 +21165,7 @@
         <v>150</v>
       </c>
       <c r="C506" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D506" s="3" t="s">
         <v>395</v>
@@ -21201,7 +21201,7 @@
     </row>
     <row r="509" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A509" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B509" s="1">
         <v>20</v>
@@ -21215,7 +21215,7 @@
     </row>
     <row r="510" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A510" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B510" s="1">
         <v>25</v>
@@ -21229,7 +21229,7 @@
     </row>
     <row r="511" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A511" s="1" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B511" s="1">
         <v>175</v>
@@ -21243,13 +21243,13 @@
     </row>
     <row r="512" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A512" s="1" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B512" s="1">
         <v>215</v>
       </c>
       <c r="C512" s="1" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D512" s="3" t="s">
         <v>20</v>
@@ -21257,7 +21257,7 @@
     </row>
     <row r="513" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A513" s="1" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B513" s="1">
         <v>150</v>
@@ -21271,7 +21271,7 @@
     </row>
     <row r="514" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A514" s="1" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B514" s="1">
         <v>60</v>
@@ -21285,7 +21285,7 @@
     </row>
     <row r="515" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A515" s="1" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B515" s="1">
         <v>350</v>
@@ -21306,7 +21306,7 @@
         <v>530</v>
       </c>
       <c r="C516" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D516" s="3" t="s">
         <v>20</v>
@@ -21405,7 +21405,7 @@
         <v>285</v>
       </c>
       <c r="C523" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="D523" s="3" t="s">
         <v>20</v>
@@ -21413,13 +21413,13 @@
     </row>
     <row r="524" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A524" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B524" s="1">
         <v>490</v>
       </c>
       <c r="C524" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D524" s="3" t="s">
         <v>20</v>
@@ -21427,13 +21427,13 @@
     </row>
     <row r="525" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A525" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B525" s="1">
         <v>5240</v>
       </c>
       <c r="C525" s="1" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D525" s="3" t="s">
         <v>20</v>
@@ -21441,13 +21441,13 @@
     </row>
     <row r="526" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A526" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B526" s="1">
         <v>6980</v>
       </c>
       <c r="C526" s="1" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D526" s="3" t="s">
         <v>20</v>
@@ -21455,7 +21455,7 @@
     </row>
     <row r="527" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A527" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B527" s="1">
         <v>40</v>
@@ -21469,13 +21469,13 @@
     </row>
     <row r="528" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A528" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B528" s="1">
         <v>195</v>
       </c>
       <c r="C528" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D528" s="3" t="s">
         <v>395</v>
@@ -21483,7 +21483,7 @@
     </row>
     <row r="529" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A529" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B529" s="1">
         <v>50</v>
@@ -21503,7 +21503,7 @@
         <v>105</v>
       </c>
       <c r="C530" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="D530" s="3" t="s">
         <v>20</v>
@@ -21545,7 +21545,7 @@
         <v>60</v>
       </c>
       <c r="C533" s="1" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D533" s="3" t="s">
         <v>402</v>
@@ -21560,7 +21560,7 @@
         <v>165</v>
       </c>
       <c r="C534" s="1" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D534" s="3" t="s">
         <v>395</v>
@@ -21610,13 +21610,13 @@
     </row>
     <row r="538" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A538" s="1" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B538" s="1">
         <v>95</v>
       </c>
       <c r="C538" s="1" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D538" s="3" t="s">
         <v>20</v>
@@ -21624,7 +21624,7 @@
     </row>
     <row r="539" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A539" s="1" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B539" s="1">
         <v>20</v>
@@ -21638,13 +21638,13 @@
     </row>
     <row r="540" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A540" s="1" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B540" s="1">
         <v>175</v>
       </c>
       <c r="C540" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D540" s="3" t="s">
         <v>20</v>
@@ -21658,7 +21658,7 @@
         <v>160</v>
       </c>
       <c r="C541" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D541" s="3" t="s">
         <v>20</v>
@@ -21692,7 +21692,7 @@
         <v>868</v>
       </c>
       <c r="C544" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D544" s="3" t="s">
         <v>20</v>
@@ -21706,7 +21706,7 @@
         <v>80</v>
       </c>
       <c r="C545" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D545" s="3" t="s">
         <v>20</v>
@@ -21790,7 +21790,7 @@
         <v>60</v>
       </c>
       <c r="C551" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D551" s="3" t="s">
         <v>395</v>
@@ -21846,7 +21846,7 @@
         <v>60</v>
       </c>
       <c r="C555" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D555" s="3" t="s">
         <v>20</v>
@@ -21959,7 +21959,7 @@
         <v>155</v>
       </c>
       <c r="C563" s="1" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D563" s="3" t="s">
         <v>20</v>
@@ -22015,7 +22015,7 @@
         <v>80</v>
       </c>
       <c r="C567" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D567" s="3" t="s">
         <v>20</v>
@@ -22114,7 +22114,7 @@
         <v>345</v>
       </c>
       <c r="C574" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D574" s="3" t="s">
         <v>35</v>
@@ -22198,7 +22198,7 @@
         <v>105</v>
       </c>
       <c r="C580" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D580" s="3" t="s">
         <v>35</v>
@@ -22381,7 +22381,7 @@
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A595" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B595" s="1">
         <v>16353</v>
@@ -22389,7 +22389,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A596" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B596" s="1">
         <f>B593-B594-B595</f>

--- a/worlds/spyro_aht/setup/Gem Research.xlsx
+++ b/worlds/spyro_aht/setup/Gem Research.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sean\Downloads\Archipelago Stuff\apworlds\PhoenixAP\worlds\spyro_aht\setup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAE3FBF1-E438-40C5-90BC-5279D589720C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58B4B889-6C5B-4C9F-85D9-730BC5B7D71F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="697" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2348,7 +2348,7 @@
     <t>HasAll('Double Jump', 'Fire Breath', 'Electric Breath')</t>
   </si>
   <si>
-    <t>Has('Double Jump', 'Electric Breath')</t>
+    <t>HasAll('Double Jump', 'Electric Breath')</t>
   </si>
 </sst>
 </file>

--- a/worlds/spyro_aht/setup/Gem Research.xlsx
+++ b/worlds/spyro_aht/setup/Gem Research.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sean\Downloads\Archipelago Stuff\apworlds\PhoenixAP\worlds\spyro_aht\setup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58B4B889-6C5B-4C9F-85D9-730BC5B7D71F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59C7FBA1-1679-4DFF-9516-8139E5B0F352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="697" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -297,7 +297,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4186" uniqueCount="684">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4180" uniqueCount="686">
   <si>
     <t>DVEntry</t>
   </si>
@@ -2186,9 +2186,6 @@
     <t>metal chests/headbash chests/and baskets using DJ</t>
   </si>
   <si>
-    <t>baskets behind lasers/headbash chest</t>
-  </si>
-  <si>
     <t>NON-BLINK ENEMIES</t>
   </si>
   <si>
@@ -2349,6 +2346,15 @@
   </si>
   <si>
     <t>HasAll('Double Jump', 'Electric Breath')</t>
+  </si>
+  <si>
+    <t>[enemy] armored middle robo-gnorc and small robo-gnorc</t>
+  </si>
+  <si>
+    <t>baskets behind lasers + headbash chest</t>
+  </si>
+  <si>
+    <t>[enemy] armored middle robo-gnorc + huge robo-gnorcs up high</t>
   </si>
 </sst>
 </file>
@@ -2715,7 +2721,7 @@
   <cols>
     <col min="1" max="1" width="41.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="98" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="107.85546875" style="1" customWidth="1"/>
     <col min="4" max="4" width="170.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="115.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -2927,7 +2933,7 @@
         <v>395</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>20</v>
@@ -2941,7 +2947,7 @@
         <v>360</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>20</v>
@@ -3941,7 +3947,7 @@
         <v>1003</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>20</v>
@@ -3955,7 +3961,7 @@
         <v>928</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>20</v>
@@ -4436,7 +4442,7 @@
         <v>675</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D123" s="3" t="s">
         <v>20</v>
@@ -4450,7 +4456,7 @@
         <v>700</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D124" s="3" t="s">
         <v>20</v>
@@ -5834,7 +5840,7 @@
         <v>755</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="D223" s="3" t="s">
         <v>20</v>
@@ -5848,7 +5854,7 @@
         <v>1435</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D224" s="3" t="s">
         <v>20</v>
@@ -6651,7 +6657,7 @@
         <v>200</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D282" s="3" t="s">
         <v>20</v>
@@ -6665,7 +6671,7 @@
         <v>200</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D283" s="3" t="s">
         <v>20</v>
@@ -7272,7 +7278,7 @@
         <v>900</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D327" s="3" t="s">
         <v>20</v>
@@ -7286,7 +7292,7 @@
         <v>800</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D328" s="3" t="s">
         <v>20</v>
@@ -7710,7 +7716,7 @@
         <v>194</v>
       </c>
       <c r="D358" s="3" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.45">
@@ -7721,10 +7727,10 @@
         <v>50</v>
       </c>
       <c r="C359" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D359" s="3" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.45">
@@ -7735,7 +7741,7 @@
         <v>100</v>
       </c>
       <c r="C360" s="1" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D360" s="3" t="s">
         <v>209</v>
@@ -8118,7 +8124,7 @@
         <v>1906</v>
       </c>
       <c r="C388" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D388" s="3" t="s">
         <v>20</v>
@@ -8132,7 +8138,7 @@
         <v>1956</v>
       </c>
       <c r="C389" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D389" s="3" t="s">
         <v>20</v>
@@ -8205,7 +8211,7 @@
         <v>50</v>
       </c>
       <c r="C394" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D394" s="3" t="s">
         <v>211</v>
@@ -8891,7 +8897,7 @@
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A444" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B444" s="1">
         <v>110</v>
@@ -8905,7 +8911,7 @@
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A445" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B445" s="1">
         <v>156</v>
@@ -8922,7 +8928,7 @@
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A446" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B446" s="1">
         <v>400</v>
@@ -8936,7 +8942,7 @@
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A447" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B447" s="1">
         <v>500</v>
@@ -8950,7 +8956,7 @@
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A448" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B448" s="1">
         <v>400</v>
@@ -8964,7 +8970,7 @@
     </row>
     <row r="449" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A449" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B449" s="1">
         <v>60</v>
@@ -8978,7 +8984,7 @@
     </row>
     <row r="450" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A450" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B450" s="1">
         <v>100</v>
@@ -8992,7 +8998,7 @@
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A451" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B451" s="1">
         <v>1000</v>
@@ -9006,7 +9012,7 @@
     </row>
     <row r="452" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A452" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B452" s="1">
         <v>450</v>
@@ -9020,7 +9026,7 @@
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A453" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B453" s="1">
         <v>50</v>
@@ -9034,13 +9040,13 @@
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A454" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B454" s="1">
         <v>950</v>
       </c>
       <c r="C454" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D454" s="3" t="s">
         <v>20</v>
@@ -9048,13 +9054,13 @@
     </row>
     <row r="455" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A455" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B455" s="1">
         <v>900</v>
       </c>
       <c r="C455" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D455" s="3" t="s">
         <v>20</v>
@@ -9062,7 +9068,7 @@
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A456" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B456" s="1">
         <v>200</v>
@@ -9689,7 +9695,7 @@
         <v>800</v>
       </c>
       <c r="C501" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D501" s="3" t="s">
         <v>20</v>
@@ -9703,7 +9709,7 @@
         <v>830</v>
       </c>
       <c r="C502" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D502" s="3" t="s">
         <v>20</v>
@@ -10369,7 +10375,7 @@
         <v>270</v>
       </c>
       <c r="C550" s="1" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="D550" s="3" t="s">
         <v>20</v>
@@ -10794,7 +10800,7 @@
         <v>443</v>
       </c>
       <c r="C581" s="1" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D581" s="3" t="s">
         <v>20</v>
@@ -10808,7 +10814,7 @@
         <v>443</v>
       </c>
       <c r="C582" s="1" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D582" s="3" t="s">
         <v>20</v>
@@ -10822,7 +10828,7 @@
         <v>50</v>
       </c>
       <c r="C583" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D583" s="3" t="s">
         <v>20</v>
@@ -10914,13 +10920,13 @@
     </row>
     <row r="590" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A590" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B590" s="1">
         <v>50</v>
       </c>
       <c r="C590" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D590" s="3" t="s">
         <v>20</v>
@@ -10928,7 +10934,7 @@
     </row>
     <row r="591" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A591" s="1" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B591" s="1">
         <v>25</v>
@@ -10942,7 +10948,7 @@
     </row>
     <row r="592" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A592" s="1" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B592" s="1">
         <v>130</v>
@@ -10956,7 +10962,7 @@
     </row>
     <row r="593" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A593" s="1" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B593" s="1">
         <v>55</v>
@@ -10970,7 +10976,7 @@
     </row>
     <row r="594" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A594" s="1" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B594" s="1">
         <v>50</v>
@@ -12202,7 +12208,7 @@
         <v>1100</v>
       </c>
       <c r="C682" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D682" s="3" t="s">
         <v>20</v>
@@ -12216,7 +12222,7 @@
         <v>900</v>
       </c>
       <c r="C683" s="1" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D683" s="3" t="s">
         <v>20</v>
@@ -12411,7 +12417,7 @@
     </row>
     <row r="698" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A698" s="1" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B698" s="1">
         <v>20</v>
@@ -12425,7 +12431,7 @@
     </row>
     <row r="699" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A699" s="1" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B699" s="1">
         <v>25</v>
@@ -12439,7 +12445,7 @@
     </row>
     <row r="700" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A700" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B700" s="1">
         <v>100</v>
@@ -12453,7 +12459,7 @@
     </row>
     <row r="701" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A701" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B701" s="1">
         <v>75</v>
@@ -12467,7 +12473,7 @@
     </row>
     <row r="702" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A702" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B702" s="1">
         <v>40</v>
@@ -12481,7 +12487,7 @@
     </row>
     <row r="703" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A703" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B703" s="1">
         <v>150</v>
@@ -12495,7 +12501,7 @@
     </row>
     <row r="704" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A704" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B704" s="1">
         <v>125</v>
@@ -12509,7 +12515,7 @@
     </row>
     <row r="705" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A705" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B705" s="1">
         <v>60</v>
@@ -12523,7 +12529,7 @@
     </row>
     <row r="706" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A706" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B706" s="1">
         <v>50</v>
@@ -12537,7 +12543,7 @@
     </row>
     <row r="707" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A707" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B707" s="1">
         <v>350</v>
@@ -12750,7 +12756,7 @@
     </row>
     <row r="722" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A722" s="1" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B722" s="1">
         <v>200</v>
@@ -12764,7 +12770,7 @@
     </row>
     <row r="723" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A723" s="1" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B723" s="1">
         <v>100</v>
@@ -12778,7 +12784,7 @@
     </row>
     <row r="724" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A724" s="1" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B724" s="1">
         <v>100</v>
@@ -12792,7 +12798,7 @@
     </row>
     <row r="725" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A725" s="1" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B725" s="1">
         <v>90</v>
@@ -12806,13 +12812,13 @@
     </row>
     <row r="726" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A726" s="1" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B726" s="1">
         <v>5240</v>
       </c>
       <c r="C726" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D726" s="3" t="s">
         <v>20</v>
@@ -12820,13 +12826,13 @@
     </row>
     <row r="727" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A727" s="1" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B727" s="1">
         <v>6980</v>
       </c>
       <c r="C727" s="1" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D727" s="3" t="s">
         <v>20</v>
@@ -12834,7 +12840,7 @@
     </row>
     <row r="728" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A728" s="1" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B728" s="1">
         <v>40</v>
@@ -12848,7 +12854,7 @@
     </row>
     <row r="729" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A729" s="1" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B729" s="1">
         <v>175</v>
@@ -12862,13 +12868,13 @@
     </row>
     <row r="730" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A730" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="B730" s="1">
+        <v>20</v>
+      </c>
+      <c r="C730" s="1" t="s">
         <v>663</v>
-      </c>
-      <c r="B730" s="1">
-        <v>20</v>
-      </c>
-      <c r="C730" s="1" t="s">
-        <v>664</v>
       </c>
       <c r="D730" s="3" t="s">
         <v>392</v>
@@ -12876,7 +12882,7 @@
     </row>
     <row r="731" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A731" s="1" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B731" s="1">
         <v>50</v>
@@ -13058,7 +13064,7 @@
     </row>
     <row r="744" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A744" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B744" s="1">
         <v>75</v>
@@ -13072,7 +13078,7 @@
     </row>
     <row r="745" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A745" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B745" s="1">
         <v>20</v>
@@ -13086,7 +13092,7 @@
     </row>
     <row r="746" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A746" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B746" s="1">
         <v>20</v>
@@ -13100,7 +13106,7 @@
     </row>
     <row r="747" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A747" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B747" s="1">
         <v>50</v>
@@ -13114,7 +13120,7 @@
     </row>
     <row r="748" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A748" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B748" s="1">
         <v>100</v>
@@ -13128,7 +13134,7 @@
     </row>
     <row r="749" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A749" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B749" s="1">
         <v>25</v>
@@ -13884,7 +13890,7 @@
         <v>510</v>
       </c>
       <c r="D803" s="3" t="s">
-        <v>393</v>
+        <v>20</v>
       </c>
     </row>
     <row r="804" spans="1:4" x14ac:dyDescent="0.45">
@@ -13968,7 +13974,7 @@
         <v>524</v>
       </c>
       <c r="D809" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="810" spans="1:4" x14ac:dyDescent="0.45">
@@ -14116,7 +14122,7 @@
     </row>
     <row r="822" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A822" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B822" s="1">
         <v>16353</v>
@@ -14124,7 +14130,7 @@
     </row>
     <row r="823" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A823" s="1" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B823" s="1">
         <f>B820-B821-B822</f>
@@ -14140,7 +14146,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABB84367-A097-4248-9984-F4697DA02168}">
-  <dimension ref="A1:D595"/>
+  <dimension ref="A1:D593"/>
   <sheetFormatPr defaultRowHeight="28.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="41.140625" style="1" bestFit="1" customWidth="1"/>
@@ -14276,7 +14282,7 @@
         <v>395</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>20</v>
@@ -14290,7 +14296,7 @@
         <v>360</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>20</v>
@@ -15000,7 +15006,7 @@
         <v>1003</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>20</v>
@@ -15014,7 +15020,7 @@
         <v>928</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>20</v>
@@ -15358,7 +15364,7 @@
         <v>675</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>20</v>
@@ -15372,7 +15378,7 @@
         <v>700</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>20</v>
@@ -16109,7 +16115,7 @@
         <v>525</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D142" s="3" t="s">
         <v>20</v>
@@ -16376,7 +16382,7 @@
         <v>755</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="D161" s="3" t="s">
         <v>20</v>
@@ -16390,7 +16396,7 @@
         <v>1435</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D162" s="3" t="s">
         <v>20</v>
@@ -16875,7 +16881,7 @@
         <v>200</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D197" s="3" t="s">
         <v>20</v>
@@ -16889,7 +16895,7 @@
         <v>200</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D198" s="3" t="s">
         <v>20</v>
@@ -16918,7 +16924,7 @@
         <v>410</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D200" s="3" t="s">
         <v>20</v>
@@ -17373,7 +17379,7 @@
         <v>900</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D233" s="3" t="s">
         <v>20</v>
@@ -17387,7 +17393,7 @@
         <v>800</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D234" s="3" t="s">
         <v>20</v>
@@ -17515,7 +17521,7 @@
         <v>606</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D243" s="3" t="s">
         <v>20</v>
@@ -17543,7 +17549,7 @@
         <v>235</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="D245" s="3" t="s">
         <v>20</v>
@@ -17645,7 +17651,7 @@
         <v>194</v>
       </c>
       <c r="D252" s="3" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.45">
@@ -17656,10 +17662,10 @@
         <v>50</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.45">
@@ -17670,7 +17676,7 @@
         <v>100</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D254" s="3" t="s">
         <v>209</v>
@@ -17888,7 +17894,7 @@
         <v>1906</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D270" s="3" t="s">
         <v>20</v>
@@ -17902,7 +17908,7 @@
         <v>1956</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D271" s="3" t="s">
         <v>20</v>
@@ -17958,7 +17964,7 @@
         <v>50</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D275" s="3" t="s">
         <v>211</v>
@@ -18028,7 +18034,7 @@
         <v>141</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D280" s="3" t="s">
         <v>22</v>
@@ -18463,7 +18469,7 @@
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A312" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B312" s="1">
         <v>110</v>
@@ -18477,7 +18483,7 @@
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A313" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B313" s="1">
         <v>656</v>
@@ -18491,7 +18497,7 @@
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A314" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B314" s="1">
         <v>1060</v>
@@ -18505,7 +18511,7 @@
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A315" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B315" s="1">
         <v>400</v>
@@ -18519,7 +18525,7 @@
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A316" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B316" s="1">
         <v>1000</v>
@@ -18533,13 +18539,13 @@
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A317" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B317" s="1">
         <v>200</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D317" s="3" t="s">
         <v>20</v>
@@ -18547,13 +18553,13 @@
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A318" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B318" s="1">
         <v>950</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D318" s="3" t="s">
         <v>20</v>
@@ -18561,13 +18567,13 @@
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A319" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B319" s="1">
         <v>900</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D319" s="3" t="s">
         <v>20</v>
@@ -19036,7 +19042,7 @@
         <v>800</v>
       </c>
       <c r="C353" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D353" s="3" t="s">
         <v>20</v>
@@ -19050,7 +19056,7 @@
         <v>830</v>
       </c>
       <c r="C354" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D354" s="3" t="s">
         <v>20</v>
@@ -19859,7 +19865,7 @@
         <v>443</v>
       </c>
       <c r="C413" s="1" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D413" s="3" t="s">
         <v>20</v>
@@ -19873,7 +19879,7 @@
         <v>443</v>
       </c>
       <c r="C414" s="1" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D414" s="3" t="s">
         <v>20</v>
@@ -19887,7 +19893,7 @@
         <v>50</v>
       </c>
       <c r="C415" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D415" s="3" t="s">
         <v>20</v>
@@ -19979,7 +19985,7 @@
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A422" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B422" s="1">
         <v>50</v>
@@ -19993,7 +19999,7 @@
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A423" s="1" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B423" s="1">
         <v>25</v>
@@ -20007,7 +20013,7 @@
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A424" s="1" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B424" s="1">
         <f>130+55+50</f>
@@ -20992,7 +20998,7 @@
         <v>1100</v>
       </c>
       <c r="C494" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D494" s="3" t="s">
         <v>20</v>
@@ -21006,7 +21012,7 @@
         <v>900</v>
       </c>
       <c r="C495" s="1" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D495" s="3" t="s">
         <v>20</v>
@@ -21173,7 +21179,7 @@
     </row>
     <row r="508" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A508" s="1" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B508" s="1">
         <v>20</v>
@@ -21187,7 +21193,7 @@
     </row>
     <row r="509" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A509" s="1" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B509" s="1">
         <v>25</v>
@@ -21201,7 +21207,7 @@
     </row>
     <row r="510" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A510" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B510" s="1">
         <v>175</v>
@@ -21215,13 +21221,13 @@
     </row>
     <row r="511" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A511" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B511" s="1">
         <v>215</v>
       </c>
       <c r="C511" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D511" s="3" t="s">
         <v>20</v>
@@ -21229,7 +21235,7 @@
     </row>
     <row r="512" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A512" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B512" s="1">
         <v>150</v>
@@ -21243,7 +21249,7 @@
     </row>
     <row r="513" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A513" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B513" s="1">
         <v>60</v>
@@ -21257,7 +21263,7 @@
     </row>
     <row r="514" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A514" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B514" s="1">
         <v>350</v>
@@ -21385,7 +21391,7 @@
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A523" s="1" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B523" s="1">
         <v>490</v>
@@ -21399,13 +21405,13 @@
     </row>
     <row r="524" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A524" s="1" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B524" s="1">
         <v>5240</v>
       </c>
       <c r="C524" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D524" s="3" t="s">
         <v>20</v>
@@ -21413,13 +21419,13 @@
     </row>
     <row r="525" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A525" s="1" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B525" s="1">
         <v>6980</v>
       </c>
       <c r="C525" s="1" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D525" s="3" t="s">
         <v>20</v>
@@ -21427,7 +21433,7 @@
     </row>
     <row r="526" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A526" s="1" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B526" s="1">
         <v>40</v>
@@ -21441,13 +21447,13 @@
     </row>
     <row r="527" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A527" s="1" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B527" s="1">
         <v>195</v>
       </c>
       <c r="C527" s="1" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D527" s="3" t="s">
         <v>392</v>
@@ -21455,7 +21461,7 @@
     </row>
     <row r="528" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A528" s="1" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B528" s="1">
         <v>50</v>
@@ -21517,7 +21523,7 @@
         <v>60</v>
       </c>
       <c r="C532" s="1" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D532" s="3" t="s">
         <v>399</v>
@@ -21532,7 +21538,7 @@
         <v>165</v>
       </c>
       <c r="C533" s="1" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D533" s="3" t="s">
         <v>392</v>
@@ -21582,13 +21588,13 @@
     </row>
     <row r="537" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A537" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B537" s="1">
         <v>95</v>
       </c>
       <c r="C537" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D537" s="3" t="s">
         <v>20</v>
@@ -21596,7 +21602,7 @@
     </row>
     <row r="538" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A538" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B538" s="1">
         <v>20</v>
@@ -21610,7 +21616,7 @@
     </row>
     <row r="539" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A539" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B539" s="1">
         <v>175</v>
@@ -22125,13 +22131,13 @@
         <v>377</v>
       </c>
       <c r="B576" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C576" s="1" t="s">
-        <v>510</v>
+        <v>683</v>
       </c>
       <c r="D576" s="3" t="s">
-        <v>393</v>
+        <v>20</v>
       </c>
     </row>
     <row r="577" spans="1:4" x14ac:dyDescent="0.45">
@@ -22139,10 +22145,10 @@
         <v>377</v>
       </c>
       <c r="B577" s="1">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="C577" s="1" t="s">
-        <v>507</v>
+        <v>24</v>
       </c>
       <c r="D577" s="3" t="s">
         <v>20</v>
@@ -22153,27 +22159,27 @@
         <v>377</v>
       </c>
       <c r="B578" s="1">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="C578" s="1" t="s">
-        <v>24</v>
+        <v>684</v>
       </c>
       <c r="D578" s="3" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="579" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A579" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B579" s="1">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="C579" s="1" t="s">
-        <v>629</v>
+        <v>378</v>
       </c>
       <c r="D579" s="3" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="580" spans="1:4" x14ac:dyDescent="0.45">
@@ -22181,10 +22187,10 @@
         <v>379</v>
       </c>
       <c r="B580" s="1">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="C580" s="1" t="s">
-        <v>378</v>
+        <v>685</v>
       </c>
       <c r="D580" s="3" t="s">
         <v>20</v>
@@ -22192,30 +22198,30 @@
     </row>
     <row r="581" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A581" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B581" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C581" s="1" t="s">
-        <v>524</v>
+        <v>510</v>
       </c>
       <c r="D581" s="3" t="s">
-        <v>22</v>
+        <v>402</v>
       </c>
     </row>
     <row r="582" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A582" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B582" s="1">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C582" s="1" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="D582" s="3" t="s">
-        <v>20</v>
+        <v>399</v>
       </c>
     </row>
     <row r="583" spans="1:4" x14ac:dyDescent="0.45">
@@ -22223,13 +22229,13 @@
         <v>380</v>
       </c>
       <c r="B583" s="1">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C583" s="1" t="s">
-        <v>510</v>
+        <v>33</v>
       </c>
       <c r="D583" s="3" t="s">
-        <v>402</v>
+        <v>35</v>
       </c>
     </row>
     <row r="584" spans="1:4" x14ac:dyDescent="0.45">
@@ -22237,13 +22243,13 @@
         <v>380</v>
       </c>
       <c r="B584" s="1">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="C584" s="1" t="s">
-        <v>517</v>
+        <v>24</v>
       </c>
       <c r="D584" s="3" t="s">
-        <v>399</v>
+        <v>27</v>
       </c>
     </row>
     <row r="585" spans="1:4" x14ac:dyDescent="0.45">
@@ -22251,13 +22257,13 @@
         <v>380</v>
       </c>
       <c r="B585" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="C585" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D585" s="3" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.45">
@@ -22265,13 +22271,13 @@
         <v>380</v>
       </c>
       <c r="B586" s="1">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="C586" s="1" t="s">
-        <v>24</v>
+        <v>506</v>
       </c>
       <c r="D586" s="3" t="s">
-        <v>27</v>
+        <v>392</v>
       </c>
     </row>
     <row r="587" spans="1:4" x14ac:dyDescent="0.45">
@@ -22282,10 +22288,10 @@
         <v>50</v>
       </c>
       <c r="C587" s="1" t="s">
-        <v>23</v>
+        <v>381</v>
       </c>
       <c r="D587" s="3" t="s">
-        <v>26</v>
+        <v>398</v>
       </c>
     </row>
     <row r="588" spans="1:4" x14ac:dyDescent="0.45">
@@ -22296,78 +22302,50 @@
         <v>20</v>
       </c>
       <c r="C588" s="1" t="s">
-        <v>506</v>
+        <v>526</v>
       </c>
       <c r="D588" s="3" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="589" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A589" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="B589" s="1">
-        <v>50</v>
-      </c>
-      <c r="C589" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="D589" s="3" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="590" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A590" s="1" t="s">
-        <v>380</v>
+        <v>407</v>
       </c>
       <c r="B590" s="1">
-        <v>20</v>
-      </c>
-      <c r="C590" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="D590" s="3" t="s">
-        <v>401</v>
+        <f>SUM(B2:B588)</f>
+        <v>141913</v>
+      </c>
+      <c r="C590" s="1" t="str">
+        <f>"should be " &amp; 'New Gems (simplified per-rule)'!B820</f>
+        <v>should be 141913</v>
+      </c>
+    </row>
+    <row r="591" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A591" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B591" s="1">
+        <v>20203</v>
       </c>
     </row>
     <row r="592" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A592" s="1" t="s">
-        <v>407</v>
+        <v>629</v>
       </c>
       <c r="B592" s="1">
-        <f>SUM(B2:B590)</f>
-        <v>141913</v>
-      </c>
-      <c r="C592" s="1" t="str">
-        <f>"should be " &amp; 'New Gems (simplified per-rule)'!B820</f>
-        <v>should be 141913</v>
+        <v>16353</v>
       </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A593" s="1" t="s">
-        <v>17</v>
+        <v>630</v>
       </c>
       <c r="B593" s="1">
-        <v>20203</v>
-      </c>
-    </row>
-    <row r="594" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A594" s="1" t="s">
-        <v>630</v>
-      </c>
-      <c r="B594" s="1">
-        <v>16353</v>
-      </c>
-    </row>
-    <row r="595" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A595" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="B595" s="1">
-        <f>B592-B593-B594</f>
+        <f>B590-B591-B592</f>
         <v>105357</v>
       </c>
-      <c r="C595" s="1" t="str">
+      <c r="C593" s="1" t="str">
         <f>"should be " &amp; 'New Gems (simplified per-rule)'!B823</f>
         <v>should be 105357</v>
       </c>

--- a/worlds/spyro_aht/setup/Gem Research.xlsx
+++ b/worlds/spyro_aht/setup/Gem Research.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sean\Downloads\Archipelago Stuff\apworlds\PhoenixAP\worlds\spyro_aht\setup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FF93797-22CD-43C8-8C5B-FCDF86CB5250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72BE1D7F-85F1-46E5-B01E-3EC70D1CE366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="697" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="697" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="New Gems (simplified per-rule)" sheetId="14" r:id="rId1"/>
@@ -297,7 +297,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4180" uniqueCount="690">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4198" uniqueCount="690">
   <si>
     <t>DVEntry</t>
   </si>
@@ -2012,15 +2012,9 @@
     <t>[enemy] archer gnorc/unarmored middle gnorc</t>
   </si>
   <si>
-    <t>baskets/dark shards</t>
-  </si>
-  <si>
     <t>[enemy] yeti/unarmored middle gnorc</t>
   </si>
   <si>
-    <t>baskets/metal chests/headbash chest and rocks/on the ground/dark shard</t>
-  </si>
-  <si>
     <t>on the ground/baskets/headbash chest/metal chests</t>
   </si>
   <si>
@@ -2367,6 +2361,12 @@
   </si>
   <si>
     <t>DVByrdUpper2</t>
+  </si>
+  <si>
+    <t>Has('Charge') | Shockwave_Rock_Monsters HasAll('Double Jump', 'Shockwave')</t>
+  </si>
+  <si>
+    <t>metal chests/baskets/headbash chests in RL entryway</t>
   </si>
 </sst>
 </file>
@@ -2728,7 +2728,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BA72872-8033-4B31-8137-7B209A06634B}">
-  <dimension ref="A1:M823"/>
+  <dimension ref="A1:M824"/>
   <sheetFormatPr defaultRowHeight="28.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="47.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -2780,7 +2780,7 @@
         <v>29</v>
       </c>
       <c r="M3" s="1">
-        <f>SUM(B$2:B$1006)-M$2-M$1</f>
+        <f>SUM(B$2:B$1007)-M$2-M$1</f>
         <v>425739</v>
       </c>
     </row>
@@ -2847,10 +2847,10 @@
         <v>500</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.45">
@@ -2945,7 +2945,7 @@
         <v>395</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>20</v>
@@ -2959,7 +2959,7 @@
         <v>360</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>20</v>
@@ -2967,16 +2967,16 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B16" s="1">
         <v>500</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.45">
@@ -3155,10 +3155,10 @@
         <v>500</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.45">
@@ -3267,10 +3267,10 @@
         <v>500</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.45">
@@ -3595,10 +3595,10 @@
         <v>500</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.45">
@@ -3945,7 +3945,7 @@
         <v>1003</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>20</v>
@@ -3959,7 +3959,7 @@
         <v>928</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>20</v>
@@ -3987,10 +3987,10 @@
         <v>500</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.45">
@@ -4009,16 +4009,16 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A91" s="1" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B91" s="1">
         <v>500</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.45">
@@ -4454,7 +4454,7 @@
         <v>675</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="D123" s="3" t="s">
         <v>20</v>
@@ -4468,7 +4468,7 @@
         <v>700</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="D124" s="3" t="s">
         <v>20</v>
@@ -5852,7 +5852,7 @@
         <v>755</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="D223" s="3" t="s">
         <v>20</v>
@@ -5866,7 +5866,7 @@
         <v>1435</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="D224" s="3" t="s">
         <v>20</v>
@@ -6403,10 +6403,10 @@
         <v>500</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="D263" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.45">
@@ -6669,7 +6669,7 @@
         <v>200</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="D282" s="3" t="s">
         <v>20</v>
@@ -6683,7 +6683,7 @@
         <v>200</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="D283" s="3" t="s">
         <v>20</v>
@@ -6809,10 +6809,10 @@
         <v>500</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="D292" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.45">
@@ -7018,7 +7018,7 @@
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A308" s="1" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B308" s="1">
         <v>347</v>
@@ -7032,21 +7032,21 @@
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A309" s="1" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B309" s="1">
         <v>1500</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="D309" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A310" s="1" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B310" s="1">
         <v>25</v>
@@ -7060,7 +7060,7 @@
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A311" s="1" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B311" s="1">
         <v>25</v>
@@ -7290,7 +7290,7 @@
         <v>900</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="D327" s="3" t="s">
         <v>20</v>
@@ -7304,7 +7304,7 @@
         <v>800</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="D328" s="3" t="s">
         <v>20</v>
@@ -7332,10 +7332,10 @@
         <v>1500</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="D330" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.45">
@@ -7627,10 +7627,10 @@
         <v>1500</v>
       </c>
       <c r="C351" s="1" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.45">
@@ -7719,13 +7719,13 @@
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A358" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B358" s="1">
         <v>100</v>
       </c>
       <c r="C358" s="1" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D358" s="3" t="s">
         <v>20</v>
@@ -7733,27 +7733,27 @@
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A359" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B359" s="1">
         <v>1500</v>
       </c>
       <c r="C359" s="1" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D359" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A360" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B360" s="1">
         <v>50</v>
       </c>
       <c r="C360" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="D360" s="3" t="s">
         <v>20</v>
@@ -8136,7 +8136,7 @@
         <v>1906</v>
       </c>
       <c r="C388" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="D388" s="3" t="s">
         <v>20</v>
@@ -8150,7 +8150,7 @@
         <v>1956</v>
       </c>
       <c r="C389" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="D389" s="3" t="s">
         <v>20</v>
@@ -8223,7 +8223,7 @@
         <v>50</v>
       </c>
       <c r="C394" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D394" s="3" t="s">
         <v>196</v>
@@ -8909,7 +8909,7 @@
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A444" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B444" s="1">
         <v>110</v>
@@ -8923,7 +8923,7 @@
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A445" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B445" s="1">
         <v>156</v>
@@ -8940,7 +8940,7 @@
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A446" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B446" s="1">
         <v>400</v>
@@ -8954,7 +8954,7 @@
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A447" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B447" s="1">
         <v>500</v>
@@ -8968,7 +8968,7 @@
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A448" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B448" s="1">
         <v>400</v>
@@ -8982,7 +8982,7 @@
     </row>
     <row r="449" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A449" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B449" s="1">
         <v>60</v>
@@ -8996,7 +8996,7 @@
     </row>
     <row r="450" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A450" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B450" s="1">
         <v>100</v>
@@ -9010,7 +9010,7 @@
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A451" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B451" s="1">
         <v>1000</v>
@@ -9024,7 +9024,7 @@
     </row>
     <row r="452" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A452" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B452" s="1">
         <v>450</v>
@@ -9038,7 +9038,7 @@
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A453" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B453" s="1">
         <v>50</v>
@@ -9052,13 +9052,13 @@
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A454" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B454" s="1">
         <v>950</v>
       </c>
       <c r="C454" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="D454" s="3" t="s">
         <v>20</v>
@@ -9066,13 +9066,13 @@
     </row>
     <row r="455" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A455" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B455" s="1">
         <v>900</v>
       </c>
       <c r="C455" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="D455" s="3" t="s">
         <v>20</v>
@@ -9080,7 +9080,7 @@
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A456" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B456" s="1">
         <v>200</v>
@@ -9248,7 +9248,7 @@
         <v>238</v>
       </c>
       <c r="D468" s="3" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.45">
@@ -9304,7 +9304,7 @@
         <v>24</v>
       </c>
       <c r="D472" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="473" spans="1:4" x14ac:dyDescent="0.45">
@@ -9318,7 +9318,7 @@
         <v>21</v>
       </c>
       <c r="D473" s="3" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="474" spans="1:4" x14ac:dyDescent="0.45">
@@ -9329,10 +9329,10 @@
         <v>1500</v>
       </c>
       <c r="C474" s="1" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="D474" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="475" spans="1:4" x14ac:dyDescent="0.45">
@@ -9374,7 +9374,7 @@
         <v>24</v>
       </c>
       <c r="D477" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.45">
@@ -9388,7 +9388,7 @@
         <v>23</v>
       </c>
       <c r="D478" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="479" spans="1:4" x14ac:dyDescent="0.45">
@@ -9402,7 +9402,7 @@
         <v>210</v>
       </c>
       <c r="D479" s="3" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="480" spans="1:4" x14ac:dyDescent="0.45">
@@ -9430,7 +9430,7 @@
         <v>162</v>
       </c>
       <c r="D481" s="3" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="482" spans="1:4" x14ac:dyDescent="0.45">
@@ -9486,7 +9486,7 @@
         <v>241</v>
       </c>
       <c r="D485" s="3" t="s">
-        <v>22</v>
+        <v>187</v>
       </c>
     </row>
     <row r="486" spans="1:4" x14ac:dyDescent="0.45">
@@ -9668,7 +9668,7 @@
         <v>244</v>
       </c>
       <c r="D498" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="499" spans="1:4" x14ac:dyDescent="0.45">
@@ -9707,7 +9707,7 @@
         <v>800</v>
       </c>
       <c r="C501" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D501" s="3" t="s">
         <v>20</v>
@@ -9721,7 +9721,7 @@
         <v>830</v>
       </c>
       <c r="C502" s="1" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="D502" s="3" t="s">
         <v>20</v>
@@ -10345,10 +10345,10 @@
         <v>1000</v>
       </c>
       <c r="C547" s="1" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="D547" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="548" spans="1:4" x14ac:dyDescent="0.45">
@@ -10359,10 +10359,10 @@
         <v>1500</v>
       </c>
       <c r="C548" s="1" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D548" s="3" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
     </row>
     <row r="549" spans="1:4" x14ac:dyDescent="0.45">
@@ -10387,7 +10387,7 @@
         <v>270</v>
       </c>
       <c r="C550" s="1" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D550" s="3" t="s">
         <v>20</v>
@@ -10457,10 +10457,10 @@
         <v>1000</v>
       </c>
       <c r="C555" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D555" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="556" spans="1:4" x14ac:dyDescent="0.45">
@@ -10546,10 +10546,10 @@
         <v>500</v>
       </c>
       <c r="C562" s="1" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="D562" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="563" spans="1:4" x14ac:dyDescent="0.45">
@@ -10675,7 +10675,7 @@
         <v>238</v>
       </c>
       <c r="D571" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="572" spans="1:4" x14ac:dyDescent="0.45">
@@ -10773,7 +10773,7 @@
         <v>466</v>
       </c>
       <c r="D578" s="3" t="s">
-        <v>22</v>
+        <v>688</v>
       </c>
     </row>
     <row r="579" spans="1:4" x14ac:dyDescent="0.45">
@@ -10812,7 +10812,7 @@
         <v>443</v>
       </c>
       <c r="C581" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="D581" s="3" t="s">
         <v>20</v>
@@ -10826,7 +10826,7 @@
         <v>443</v>
       </c>
       <c r="C582" s="1" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="D582" s="3" t="s">
         <v>20</v>
@@ -10840,7 +10840,7 @@
         <v>50</v>
       </c>
       <c r="C583" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D583" s="3" t="s">
         <v>20</v>
@@ -10932,13 +10932,13 @@
     </row>
     <row r="590" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A590" s="1" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B590" s="1">
         <v>50</v>
       </c>
       <c r="C590" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D590" s="3" t="s">
         <v>20</v>
@@ -10946,7 +10946,7 @@
     </row>
     <row r="591" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A591" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B591" s="1">
         <v>25</v>
@@ -10960,7 +10960,7 @@
     </row>
     <row r="592" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A592" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B592" s="1">
         <v>130</v>
@@ -10974,7 +10974,7 @@
     </row>
     <row r="593" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A593" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B593" s="1">
         <v>55</v>
@@ -10988,7 +10988,7 @@
     </row>
     <row r="594" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A594" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B594" s="1">
         <v>50</v>
@@ -11705,7 +11705,7 @@
         <v>238</v>
       </c>
       <c r="D645" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="646" spans="1:4" x14ac:dyDescent="0.45">
@@ -11719,7 +11719,7 @@
         <v>308</v>
       </c>
       <c r="D646" s="3" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="647" spans="1:4" x14ac:dyDescent="0.45">
@@ -11733,7 +11733,7 @@
         <v>470</v>
       </c>
       <c r="D647" s="3" t="s">
-        <v>22</v>
+        <v>688</v>
       </c>
     </row>
     <row r="648" spans="1:4" x14ac:dyDescent="0.45">
@@ -11884,10 +11884,10 @@
         <v>500</v>
       </c>
       <c r="C658" s="1" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="D658" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="659" spans="1:4" x14ac:dyDescent="0.45">
@@ -12220,7 +12220,7 @@
         <v>1100</v>
       </c>
       <c r="C682" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="D682" s="3" t="s">
         <v>20</v>
@@ -12234,7 +12234,7 @@
         <v>900</v>
       </c>
       <c r="C683" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="D683" s="3" t="s">
         <v>20</v>
@@ -12429,7 +12429,7 @@
     </row>
     <row r="698" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A698" s="1" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="B698" s="1">
         <v>20</v>
@@ -12443,7 +12443,7 @@
     </row>
     <row r="699" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A699" s="1" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="B699" s="1">
         <v>25</v>
@@ -12457,7 +12457,7 @@
     </row>
     <row r="700" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A700" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B700" s="1">
         <v>100</v>
@@ -12471,7 +12471,7 @@
     </row>
     <row r="701" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A701" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B701" s="1">
         <v>75</v>
@@ -12485,7 +12485,7 @@
     </row>
     <row r="702" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A702" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B702" s="1">
         <v>40</v>
@@ -12499,7 +12499,7 @@
     </row>
     <row r="703" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A703" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B703" s="1">
         <v>150</v>
@@ -12513,7 +12513,7 @@
     </row>
     <row r="704" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A704" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B704" s="1">
         <v>125</v>
@@ -12527,7 +12527,7 @@
     </row>
     <row r="705" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A705" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B705" s="1">
         <v>60</v>
@@ -12541,7 +12541,7 @@
     </row>
     <row r="706" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A706" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B706" s="1">
         <v>50</v>
@@ -12555,7 +12555,7 @@
     </row>
     <row r="707" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A707" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B707" s="1">
         <v>350</v>
@@ -12606,10 +12606,10 @@
         <v>1500</v>
       </c>
       <c r="C710" s="1" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="D710" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="711" spans="1:5" x14ac:dyDescent="0.45">
@@ -12768,7 +12768,7 @@
     </row>
     <row r="722" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A722" s="1" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B722" s="1">
         <v>200</v>
@@ -12782,7 +12782,7 @@
     </row>
     <row r="723" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A723" s="1" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B723" s="1">
         <v>100</v>
@@ -12796,7 +12796,7 @@
     </row>
     <row r="724" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A724" s="1" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B724" s="1">
         <v>100</v>
@@ -12810,7 +12810,7 @@
     </row>
     <row r="725" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A725" s="1" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B725" s="1">
         <v>90</v>
@@ -12824,13 +12824,13 @@
     </row>
     <row r="726" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A726" s="1" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B726" s="1">
         <v>5240</v>
       </c>
       <c r="C726" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="D726" s="3" t="s">
         <v>20</v>
@@ -12838,13 +12838,13 @@
     </row>
     <row r="727" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A727" s="1" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B727" s="1">
         <v>6980</v>
       </c>
       <c r="C727" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="D727" s="3" t="s">
         <v>20</v>
@@ -12852,7 +12852,7 @@
     </row>
     <row r="728" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A728" s="1" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B728" s="1">
         <v>40</v>
@@ -12866,7 +12866,7 @@
     </row>
     <row r="729" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A729" s="1" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B729" s="1">
         <v>175</v>
@@ -12880,13 +12880,13 @@
     </row>
     <row r="730" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A730" s="1" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B730" s="1">
         <v>20</v>
       </c>
       <c r="C730" s="1" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D730" s="3" t="s">
         <v>368</v>
@@ -12894,7 +12894,7 @@
     </row>
     <row r="731" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A731" s="1" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B731" s="1">
         <v>50</v>
@@ -12942,10 +12942,10 @@
         <v>1500</v>
       </c>
       <c r="C734" s="1" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="D734" s="3" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
     </row>
     <row r="735" spans="1:4" x14ac:dyDescent="0.45">
@@ -13076,7 +13076,7 @@
     </row>
     <row r="744" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A744" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B744" s="1">
         <v>75</v>
@@ -13090,7 +13090,7 @@
     </row>
     <row r="745" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A745" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B745" s="1">
         <v>20</v>
@@ -13104,7 +13104,7 @@
     </row>
     <row r="746" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A746" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B746" s="1">
         <v>20</v>
@@ -13118,7 +13118,7 @@
     </row>
     <row r="747" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A747" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B747" s="1">
         <v>50</v>
@@ -13132,7 +13132,7 @@
     </row>
     <row r="748" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A748" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B748" s="1">
         <v>100</v>
@@ -13146,7 +13146,7 @@
     </row>
     <row r="749" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A749" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B749" s="1">
         <v>25</v>
@@ -13216,21 +13216,21 @@
     </row>
     <row r="754" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A754" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
+      </c>
+      <c r="B754" s="1">
+        <v>260</v>
+      </c>
+      <c r="C754" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="D754" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="755" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A755" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B755" s="1">
-        <v>225</v>
-      </c>
-      <c r="C755" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D755" s="3" t="s">
-        <v>20</v>
+        <v>335</v>
       </c>
     </row>
     <row r="756" spans="1:4" x14ac:dyDescent="0.45">
@@ -13238,10 +13238,10 @@
         <v>10</v>
       </c>
       <c r="B756" s="1">
-        <v>475</v>
+        <v>175</v>
       </c>
       <c r="C756" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D756" s="3" t="s">
         <v>20</v>
@@ -13252,10 +13252,10 @@
         <v>10</v>
       </c>
       <c r="B757" s="1">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="C757" s="1" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="D757" s="3" t="s">
         <v>20</v>
@@ -13266,10 +13266,10 @@
         <v>10</v>
       </c>
       <c r="B758" s="1">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="C758" s="1" t="s">
-        <v>19</v>
+        <v>78</v>
       </c>
       <c r="D758" s="3" t="s">
         <v>20</v>
@@ -13280,10 +13280,10 @@
         <v>10</v>
       </c>
       <c r="B759" s="1">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="C759" s="1" t="s">
-        <v>482</v>
+        <v>19</v>
       </c>
       <c r="D759" s="3" t="s">
         <v>20</v>
@@ -13297,7 +13297,7 @@
         <v>40</v>
       </c>
       <c r="C760" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D760" s="3" t="s">
         <v>20</v>
@@ -13308,13 +13308,13 @@
         <v>10</v>
       </c>
       <c r="B761" s="1">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="C761" s="1" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="D761" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="762" spans="1:4" x14ac:dyDescent="0.45">
@@ -13322,10 +13322,10 @@
         <v>10</v>
       </c>
       <c r="B762" s="1">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="C762" s="1" t="s">
-        <v>336</v>
+        <v>485</v>
       </c>
       <c r="D762" s="3" t="s">
         <v>22</v>
@@ -13336,10 +13336,10 @@
         <v>10</v>
       </c>
       <c r="B763" s="1">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C763" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D763" s="3" t="s">
         <v>22</v>
@@ -13347,16 +13347,16 @@
     </row>
     <row r="764" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A764" s="1" t="s">
-        <v>338</v>
+        <v>10</v>
       </c>
       <c r="B764" s="1">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C764" s="1" t="s">
-        <v>488</v>
+        <v>337</v>
       </c>
       <c r="D764" s="3" t="s">
-        <v>377</v>
+        <v>22</v>
       </c>
     </row>
     <row r="765" spans="1:4" x14ac:dyDescent="0.45">
@@ -13364,13 +13364,13 @@
         <v>338</v>
       </c>
       <c r="B765" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C765" s="1" t="s">
-        <v>339</v>
+        <v>488</v>
       </c>
       <c r="D765" s="3" t="s">
-        <v>35</v>
+        <v>377</v>
       </c>
     </row>
     <row r="766" spans="1:4" x14ac:dyDescent="0.45">
@@ -13378,13 +13378,13 @@
         <v>338</v>
       </c>
       <c r="B766" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C766" s="1" t="s">
-        <v>489</v>
+        <v>339</v>
       </c>
       <c r="D766" s="3" t="s">
-        <v>368</v>
+        <v>35</v>
       </c>
     </row>
     <row r="767" spans="1:4" x14ac:dyDescent="0.45">
@@ -13395,7 +13395,7 @@
         <v>20</v>
       </c>
       <c r="C767" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D767" s="3" t="s">
         <v>368</v>
@@ -13406,13 +13406,13 @@
         <v>338</v>
       </c>
       <c r="B768" s="1">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="C768" s="1" t="s">
-        <v>341</v>
+        <v>490</v>
       </c>
       <c r="D768" s="3" t="s">
-        <v>27</v>
+        <v>368</v>
       </c>
     </row>
     <row r="769" spans="1:4" x14ac:dyDescent="0.45">
@@ -13420,13 +13420,13 @@
         <v>338</v>
       </c>
       <c r="B769" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="C769" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D769" s="3" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="770" spans="1:4" x14ac:dyDescent="0.45">
@@ -13434,27 +13434,27 @@
         <v>338</v>
       </c>
       <c r="B770" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C770" s="1" t="s">
-        <v>491</v>
+        <v>340</v>
       </c>
       <c r="D770" s="3" t="s">
-        <v>368</v>
+        <v>35</v>
       </c>
     </row>
     <row r="771" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A771" s="1" t="s">
-        <v>13</v>
+        <v>338</v>
       </c>
       <c r="B771" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C771" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D771" s="3" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
     </row>
     <row r="772" spans="1:4" x14ac:dyDescent="0.45">
@@ -13462,13 +13462,13 @@
         <v>13</v>
       </c>
       <c r="B772" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="C772" s="1" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="D772" s="3" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="773" spans="1:4" x14ac:dyDescent="0.45">
@@ -13476,27 +13476,27 @@
         <v>13</v>
       </c>
       <c r="B773" s="1">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="C773" s="1" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="D773" s="3" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
     </row>
     <row r="774" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A774" s="1" t="s">
-        <v>342</v>
+        <v>13</v>
       </c>
       <c r="B774" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C774" s="1" t="s">
-        <v>492</v>
+        <v>481</v>
       </c>
       <c r="D774" s="3" t="s">
-        <v>20</v>
+        <v>368</v>
       </c>
     </row>
     <row r="775" spans="1:4" x14ac:dyDescent="0.45">
@@ -13504,10 +13504,10 @@
         <v>342</v>
       </c>
       <c r="B775" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C775" s="1" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="D775" s="3" t="s">
         <v>20</v>
@@ -13518,10 +13518,10 @@
         <v>342</v>
       </c>
       <c r="B776" s="1">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C776" s="1" t="s">
-        <v>103</v>
+        <v>481</v>
       </c>
       <c r="D776" s="3" t="s">
         <v>20</v>
@@ -13532,13 +13532,13 @@
         <v>342</v>
       </c>
       <c r="B777" s="1">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C777" s="1" t="s">
-        <v>493</v>
+        <v>103</v>
       </c>
       <c r="D777" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="778" spans="1:4" x14ac:dyDescent="0.45">
@@ -13546,13 +13546,13 @@
         <v>342</v>
       </c>
       <c r="B778" s="1">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="C778" s="1" t="s">
-        <v>343</v>
+        <v>493</v>
       </c>
       <c r="D778" s="3" t="s">
-        <v>201</v>
+        <v>22</v>
       </c>
     </row>
     <row r="779" spans="1:4" x14ac:dyDescent="0.45">
@@ -13560,10 +13560,10 @@
         <v>342</v>
       </c>
       <c r="B779" s="1">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="C779" s="1" t="s">
-        <v>494</v>
+        <v>343</v>
       </c>
       <c r="D779" s="3" t="s">
         <v>201</v>
@@ -13574,27 +13574,27 @@
         <v>342</v>
       </c>
       <c r="B780" s="1">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C780" s="1" t="s">
-        <v>344</v>
+        <v>494</v>
       </c>
       <c r="D780" s="3" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
     </row>
     <row r="781" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A781" s="1" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B781" s="1">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="C781" s="1" t="s">
-        <v>485</v>
+        <v>344</v>
       </c>
       <c r="D781" s="3" t="s">
-        <v>22</v>
+        <v>195</v>
       </c>
     </row>
     <row r="782" spans="1:4" x14ac:dyDescent="0.45">
@@ -13602,24 +13602,24 @@
         <v>345</v>
       </c>
       <c r="B782" s="1">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="C782" s="1" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="D782" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="783" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A783" s="1" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B783" s="1">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C783" s="1" t="s">
-        <v>23</v>
+        <v>481</v>
       </c>
       <c r="D783" s="3" t="s">
         <v>20</v>
@@ -13630,10 +13630,10 @@
         <v>348</v>
       </c>
       <c r="B784" s="1">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="C784" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D784" s="3" t="s">
         <v>20</v>
@@ -13644,10 +13644,10 @@
         <v>348</v>
       </c>
       <c r="B785" s="1">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="C785" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D785" s="3" t="s">
         <v>20</v>
@@ -13655,27 +13655,27 @@
     </row>
     <row r="786" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A786" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B786" s="1">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C786" s="1" t="s">
-        <v>492</v>
+        <v>33</v>
       </c>
       <c r="D786" s="3" t="s">
-        <v>374</v>
+        <v>20</v>
       </c>
     </row>
     <row r="787" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A787" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B787" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="C787" s="1" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="D787" s="3" t="s">
         <v>374</v>
@@ -13686,27 +13686,27 @@
         <v>347</v>
       </c>
       <c r="B788" s="1">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C788" s="1" t="s">
-        <v>495</v>
+        <v>482</v>
       </c>
       <c r="D788" s="3" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
     </row>
     <row r="789" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A789" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B789" s="1">
         <v>40</v>
       </c>
       <c r="C789" s="1" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="D789" s="3" t="s">
-        <v>20</v>
+        <v>368</v>
       </c>
     </row>
     <row r="790" spans="1:4" x14ac:dyDescent="0.45">
@@ -13717,7 +13717,7 @@
         <v>40</v>
       </c>
       <c r="C790" s="1" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="D790" s="3" t="s">
         <v>20</v>
@@ -13728,10 +13728,10 @@
         <v>349</v>
       </c>
       <c r="B791" s="1">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C791" s="1" t="s">
-        <v>24</v>
+        <v>495</v>
       </c>
       <c r="D791" s="3" t="s">
         <v>20</v>
@@ -13742,13 +13742,13 @@
         <v>349</v>
       </c>
       <c r="B792" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="C792" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D792" s="3" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="793" spans="1:4" x14ac:dyDescent="0.45">
@@ -13756,10 +13756,10 @@
         <v>349</v>
       </c>
       <c r="B793" s="1">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C793" s="1" t="s">
-        <v>496</v>
+        <v>33</v>
       </c>
       <c r="D793" s="3" t="s">
         <v>35</v>
@@ -13767,16 +13767,16 @@
     </row>
     <row r="794" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A794" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B794" s="1">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="C794" s="1" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="D794" s="3" t="s">
-        <v>374</v>
+        <v>35</v>
       </c>
     </row>
     <row r="795" spans="1:4" x14ac:dyDescent="0.45">
@@ -13784,13 +13784,13 @@
         <v>350</v>
       </c>
       <c r="B795" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="C795" s="1" t="s">
-        <v>33</v>
+        <v>492</v>
       </c>
       <c r="D795" s="3" t="s">
-        <v>35</v>
+        <v>374</v>
       </c>
     </row>
     <row r="796" spans="1:4" x14ac:dyDescent="0.45">
@@ -13798,13 +13798,13 @@
         <v>350</v>
       </c>
       <c r="B796" s="1">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="C796" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D796" s="3" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="797" spans="1:4" x14ac:dyDescent="0.45">
@@ -13812,13 +13812,13 @@
         <v>350</v>
       </c>
       <c r="B797" s="1">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="C797" s="1" t="s">
-        <v>497</v>
+        <v>24</v>
       </c>
       <c r="D797" s="3" t="s">
-        <v>377</v>
+        <v>27</v>
       </c>
     </row>
     <row r="798" spans="1:4" x14ac:dyDescent="0.45">
@@ -13826,13 +13826,13 @@
         <v>350</v>
       </c>
       <c r="B798" s="1">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="C798" s="1" t="s">
-        <v>351</v>
+        <v>497</v>
       </c>
       <c r="D798" s="3" t="s">
-        <v>35</v>
+        <v>377</v>
       </c>
     </row>
     <row r="799" spans="1:4" x14ac:dyDescent="0.45">
@@ -13840,10 +13840,10 @@
         <v>350</v>
       </c>
       <c r="B799" s="1">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C799" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D799" s="3" t="s">
         <v>35</v>
@@ -13854,10 +13854,10 @@
         <v>350</v>
       </c>
       <c r="B800" s="1">
-        <v>175</v>
+        <v>60</v>
       </c>
       <c r="C800" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D800" s="3" t="s">
         <v>35</v>
@@ -13868,13 +13868,13 @@
         <v>350</v>
       </c>
       <c r="B801" s="1">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="C801" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D801" s="3" t="s">
-        <v>199</v>
+        <v>35</v>
       </c>
     </row>
     <row r="802" spans="1:4" x14ac:dyDescent="0.45">
@@ -13882,27 +13882,27 @@
         <v>350</v>
       </c>
       <c r="B802" s="1">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C802" s="1" t="s">
-        <v>498</v>
+        <v>354</v>
       </c>
       <c r="D802" s="3" t="s">
-        <v>375</v>
+        <v>199</v>
       </c>
     </row>
     <row r="803" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A803" s="1" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="B803" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C803" s="1" t="s">
-        <v>485</v>
+        <v>498</v>
       </c>
       <c r="D803" s="3" t="s">
-        <v>20</v>
+        <v>375</v>
       </c>
     </row>
     <row r="804" spans="1:4" x14ac:dyDescent="0.45">
@@ -13913,7 +13913,7 @@
         <v>20</v>
       </c>
       <c r="C804" s="1" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="D804" s="3" t="s">
         <v>20</v>
@@ -13924,10 +13924,10 @@
         <v>355</v>
       </c>
       <c r="B805" s="1">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="C805" s="1" t="s">
-        <v>24</v>
+        <v>482</v>
       </c>
       <c r="D805" s="3" t="s">
         <v>20</v>
@@ -13941,10 +13941,10 @@
         <v>75</v>
       </c>
       <c r="C806" s="1" t="s">
-        <v>372</v>
+        <v>24</v>
       </c>
       <c r="D806" s="3" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="807" spans="1:4" x14ac:dyDescent="0.45">
@@ -13952,10 +13952,10 @@
         <v>355</v>
       </c>
       <c r="B807" s="1">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="C807" s="1" t="s">
-        <v>33</v>
+        <v>372</v>
       </c>
       <c r="D807" s="3" t="s">
         <v>35</v>
@@ -13963,16 +13963,16 @@
     </row>
     <row r="808" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A808" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B808" s="1">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="C808" s="1" t="s">
-        <v>356</v>
+        <v>33</v>
       </c>
       <c r="D808" s="3" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="809" spans="1:4" x14ac:dyDescent="0.45">
@@ -13980,10 +13980,10 @@
         <v>357</v>
       </c>
       <c r="B809" s="1">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="C809" s="1" t="s">
-        <v>499</v>
+        <v>356</v>
       </c>
       <c r="D809" s="3" t="s">
         <v>20</v>
@@ -13994,10 +13994,10 @@
         <v>357</v>
       </c>
       <c r="B810" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C810" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D810" s="3" t="s">
         <v>20</v>
@@ -14005,16 +14005,16 @@
     </row>
     <row r="811" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A811" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B811" s="1">
         <v>40</v>
       </c>
       <c r="C811" s="1" t="s">
-        <v>485</v>
+        <v>500</v>
       </c>
       <c r="D811" s="3" t="s">
-        <v>377</v>
+        <v>20</v>
       </c>
     </row>
     <row r="812" spans="1:4" x14ac:dyDescent="0.45">
@@ -14022,13 +14022,13 @@
         <v>358</v>
       </c>
       <c r="B812" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="C812" s="1" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="D812" s="3" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="813" spans="1:4" x14ac:dyDescent="0.45">
@@ -14036,13 +14036,13 @@
         <v>358</v>
       </c>
       <c r="B813" s="1">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="C813" s="1" t="s">
-        <v>33</v>
+        <v>492</v>
       </c>
       <c r="D813" s="3" t="s">
-        <v>35</v>
+        <v>374</v>
       </c>
     </row>
     <row r="814" spans="1:4" x14ac:dyDescent="0.45">
@@ -14050,13 +14050,13 @@
         <v>358</v>
       </c>
       <c r="B814" s="1">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="C814" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D814" s="3" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="815" spans="1:4" x14ac:dyDescent="0.45">
@@ -14064,13 +14064,13 @@
         <v>358</v>
       </c>
       <c r="B815" s="1">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="C815" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D815" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="816" spans="1:4" x14ac:dyDescent="0.45">
@@ -14078,13 +14078,13 @@
         <v>358</v>
       </c>
       <c r="B816" s="1">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="C816" s="1" t="s">
-        <v>481</v>
+        <v>23</v>
       </c>
       <c r="D816" s="3" t="s">
-        <v>368</v>
+        <v>26</v>
       </c>
     </row>
     <row r="817" spans="1:4" x14ac:dyDescent="0.45">
@@ -14092,13 +14092,13 @@
         <v>358</v>
       </c>
       <c r="B817" s="1">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="C817" s="1" t="s">
-        <v>359</v>
+        <v>481</v>
       </c>
       <c r="D817" s="3" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
     </row>
     <row r="818" spans="1:4" x14ac:dyDescent="0.45">
@@ -14106,46 +14106,60 @@
         <v>358</v>
       </c>
       <c r="B818" s="1">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="C818" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D818" s="3" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="819" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A819" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B819" s="1">
+        <v>20</v>
+      </c>
+      <c r="C819" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="D818" s="3" t="s">
+      <c r="D819" s="3" t="s">
         <v>376</v>
-      </c>
-    </row>
-    <row r="820" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A820" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="B820" s="1">
-        <f>SUM(B2:B818)</f>
-        <v>141913</v>
       </c>
     </row>
     <row r="821" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A821" s="1" t="s">
-        <v>17</v>
+        <v>382</v>
       </c>
       <c r="B821" s="1">
-        <v>20203</v>
+        <f>SUM(B2:B819)</f>
+        <v>141913</v>
       </c>
     </row>
     <row r="822" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A822" s="1" t="s">
-        <v>603</v>
+        <v>17</v>
       </c>
       <c r="B822" s="1">
-        <v>16353</v>
+        <v>20203</v>
       </c>
     </row>
     <row r="823" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A823" s="1" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="B823" s="1">
-        <f>B820-B821-B822</f>
+        <v>16353</v>
+      </c>
+    </row>
+    <row r="824" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A824" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="B824" s="1">
+        <f>B821-B822-B823</f>
         <v>105357</v>
       </c>
     </row>
@@ -14158,14 +14172,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABB84367-A097-4248-9984-F4697DA02168}">
-  <dimension ref="A1:D593"/>
+  <dimension ref="A1:D598"/>
   <sheetFormatPr defaultRowHeight="28.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="47.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="106.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="205.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="1"/>
+    <col min="5" max="5" width="33.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="38.7109375" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
@@ -14251,10 +14268,10 @@
         <v>500</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
@@ -14294,7 +14311,7 @@
         <v>395</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>20</v>
@@ -14308,7 +14325,7 @@
         <v>360</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>20</v>
@@ -14316,16 +14333,16 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B12" s="1">
         <v>500</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
@@ -14408,10 +14425,10 @@
         <v>500</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
@@ -14479,10 +14496,10 @@
         <v>500</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.45">
@@ -14724,10 +14741,10 @@
         <v>500</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.45">
@@ -15004,7 +15021,7 @@
         <v>1003</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>20</v>
@@ -15018,7 +15035,7 @@
         <v>928</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>20</v>
@@ -15047,24 +15064,24 @@
         <v>500</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A65" s="1" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B65" s="1">
         <v>500</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.45">
@@ -15376,7 +15393,7 @@
         <v>675</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>20</v>
@@ -15390,7 +15407,7 @@
         <v>700</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>20</v>
@@ -16127,7 +16144,7 @@
         <v>525</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="D142" s="3" t="s">
         <v>20</v>
@@ -16394,7 +16411,7 @@
         <v>755</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="D161" s="3" t="s">
         <v>20</v>
@@ -16408,7 +16425,7 @@
         <v>1435</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="D162" s="3" t="s">
         <v>20</v>
@@ -16794,10 +16811,10 @@
         <v>500</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.45">
@@ -16893,7 +16910,7 @@
         <v>200</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="D197" s="3" t="s">
         <v>20</v>
@@ -16907,7 +16924,7 @@
         <v>200</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="D198" s="3" t="s">
         <v>20</v>
@@ -16936,7 +16953,7 @@
         <v>410</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="D200" s="3" t="s">
         <v>20</v>
@@ -16978,10 +16995,10 @@
         <v>500</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.45">
@@ -17161,7 +17178,7 @@
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A217" s="1" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B217" s="1">
         <v>397</v>
@@ -17175,16 +17192,16 @@
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A218" s="1" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B218" s="1">
         <v>1500</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.45">
@@ -17391,7 +17408,7 @@
         <v>900</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="D233" s="3" t="s">
         <v>20</v>
@@ -17405,7 +17422,7 @@
         <v>800</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="D234" s="3" t="s">
         <v>20</v>
@@ -17433,10 +17450,10 @@
         <v>1500</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.45">
@@ -17533,7 +17550,7 @@
         <v>606</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="D243" s="3" t="s">
         <v>20</v>
@@ -17561,7 +17578,7 @@
         <v>235</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="D245" s="3" t="s">
         <v>20</v>
@@ -17590,10 +17607,10 @@
         <v>1500</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.45">
@@ -17654,13 +17671,13 @@
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A252" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B252" s="1">
         <v>100</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D252" s="3" t="s">
         <v>20</v>
@@ -17668,27 +17685,27 @@
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A253" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B253" s="1">
         <v>1500</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A254" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B254" s="1">
         <v>50</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="D254" s="3" t="s">
         <v>20</v>
@@ -17906,7 +17923,7 @@
         <v>1906</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="D270" s="3" t="s">
         <v>20</v>
@@ -17920,7 +17937,7 @@
         <v>1956</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="D271" s="3" t="s">
         <v>20</v>
@@ -17976,7 +17993,7 @@
         <v>50</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D275" s="3" t="s">
         <v>196</v>
@@ -18046,7 +18063,7 @@
         <v>141</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="D280" s="3" t="s">
         <v>22</v>
@@ -18481,7 +18498,7 @@
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A312" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B312" s="1">
         <v>110</v>
@@ -18495,7 +18512,7 @@
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A313" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B313" s="1">
         <v>656</v>
@@ -18509,7 +18526,7 @@
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A314" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B314" s="1">
         <v>1060</v>
@@ -18523,7 +18540,7 @@
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A315" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B315" s="1">
         <v>400</v>
@@ -18537,7 +18554,7 @@
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A316" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B316" s="1">
         <v>1000</v>
@@ -18551,13 +18568,13 @@
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A317" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B317" s="1">
         <v>200</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D317" s="3" t="s">
         <v>20</v>
@@ -18565,13 +18582,13 @@
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A318" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B318" s="1">
         <v>950</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="D318" s="3" t="s">
         <v>20</v>
@@ -18579,13 +18596,13 @@
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A319" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B319" s="1">
         <v>900</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="D319" s="3" t="s">
         <v>20</v>
@@ -18747,7 +18764,7 @@
         <v>238</v>
       </c>
       <c r="D331" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.45">
@@ -18783,13 +18800,13 @@
         <v>239</v>
       </c>
       <c r="B334" s="1">
-        <v>175</v>
+        <v>75</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>571</v>
+        <v>24</v>
       </c>
       <c r="D334" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.45">
@@ -18797,27 +18814,27 @@
         <v>239</v>
       </c>
       <c r="B335" s="1">
-        <v>1500</v>
+        <v>100</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>675</v>
+        <v>21</v>
       </c>
       <c r="D335" s="3" t="s">
-        <v>684</v>
+        <v>25</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A336" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B336" s="1">
-        <v>400</v>
+        <v>1500</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>460</v>
+        <v>673</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>368</v>
+        <v>682</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.45">
@@ -18825,13 +18842,13 @@
         <v>240</v>
       </c>
       <c r="B337" s="1">
-        <v>39</v>
+        <v>400</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>572</v>
+        <v>460</v>
       </c>
       <c r="D337" s="3" t="s">
-        <v>42</v>
+        <v>368</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.45">
@@ -18839,14 +18856,13 @@
         <v>240</v>
       </c>
       <c r="B338" s="1">
-        <f>250+130+95</f>
-        <v>475</v>
+        <v>39</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="D338" s="3" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.45">
@@ -18854,13 +18870,13 @@
         <v>240</v>
       </c>
       <c r="B339" s="1">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>383</v>
+        <v>24</v>
       </c>
       <c r="D339" s="3" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.45">
@@ -18868,13 +18884,13 @@
         <v>240</v>
       </c>
       <c r="B340" s="1">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>436</v>
+        <v>23</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.45">
@@ -18882,98 +18898,98 @@
         <v>240</v>
       </c>
       <c r="B341" s="1">
-        <v>25</v>
+        <v>130</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>241</v>
+        <v>210</v>
       </c>
       <c r="D341" s="3" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A342" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B342" s="1">
+        <v>45</v>
+      </c>
+      <c r="C342" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D342" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A343" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B343" s="1">
+        <v>50</v>
+      </c>
+      <c r="C343" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D343" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A344" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B344" s="1">
+        <v>20</v>
+      </c>
+      <c r="C344" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D344" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A345" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B345" s="1">
+        <v>40</v>
+      </c>
+      <c r="C345" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="D345" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A346" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B346" s="1">
+        <v>25</v>
+      </c>
+      <c r="C346" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D346" s="3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A347" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B342" s="1">
+      <c r="B347" s="1">
         <f>28+100+30+50</f>
         <v>208</v>
       </c>
-      <c r="C342" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="D342" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A343" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="B343" s="1">
-        <v>130</v>
-      </c>
-      <c r="C343" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D343" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A344" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="B344" s="1">
-        <v>300</v>
-      </c>
-      <c r="C344" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D344" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A345" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="B345" s="1">
-        <v>200</v>
-      </c>
-      <c r="C345" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D345" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A346" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="B346" s="1">
-        <v>300</v>
-      </c>
-      <c r="C346" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D346" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A347" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="B347" s="1">
-        <v>25</v>
-      </c>
       <c r="C347" s="1" t="s">
-        <v>462</v>
+        <v>572</v>
       </c>
       <c r="D347" s="3" t="s">
-        <v>190</v>
+        <v>20</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.45">
@@ -18981,13 +18997,13 @@
         <v>243</v>
       </c>
       <c r="B348" s="1">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C348" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.45">
@@ -18995,13 +19011,13 @@
         <v>243</v>
       </c>
       <c r="B349" s="1">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="C349" s="1" t="s">
-        <v>383</v>
+        <v>24</v>
       </c>
       <c r="D349" s="3" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.45">
@@ -19009,13 +19025,13 @@
         <v>243</v>
       </c>
       <c r="B350" s="1">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>244</v>
+        <v>210</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>684</v>
+        <v>35</v>
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.45">
@@ -19023,13 +19039,13 @@
         <v>243</v>
       </c>
       <c r="B351" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="C351" s="1" t="s">
-        <v>460</v>
+        <v>21</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>368</v>
+        <v>25</v>
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.45">
@@ -19037,13 +19053,13 @@
         <v>243</v>
       </c>
       <c r="B352" s="1">
-        <v>140</v>
+        <v>25</v>
       </c>
       <c r="C352" s="1" t="s">
-        <v>575</v>
+        <v>462</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>42</v>
+        <v>190</v>
       </c>
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.45">
@@ -19051,13 +19067,13 @@
         <v>243</v>
       </c>
       <c r="B353" s="1">
-        <v>800</v>
+        <v>125</v>
       </c>
       <c r="C353" s="1" t="s">
-        <v>629</v>
+        <v>23</v>
       </c>
       <c r="D353" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.45">
@@ -19065,94 +19081,94 @@
         <v>243</v>
       </c>
       <c r="B354" s="1">
-        <v>830</v>
+        <v>40</v>
       </c>
       <c r="C354" s="1" t="s">
-        <v>630</v>
+        <v>383</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A355" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B355" s="1">
-        <v>1500</v>
+        <v>50</v>
       </c>
       <c r="C355" s="1" t="s">
-        <v>528</v>
+        <v>244</v>
       </c>
       <c r="D355" s="3" t="s">
-        <v>20</v>
+        <v>682</v>
       </c>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A356" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B356" s="1">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="C356" s="1" t="s">
-        <v>576</v>
+        <v>460</v>
       </c>
       <c r="D356" s="3" t="s">
-        <v>20</v>
+        <v>368</v>
       </c>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A357" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B357" s="1">
-        <v>390</v>
+        <v>140</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>280</v>
+        <v>573</v>
       </c>
       <c r="D357" s="3" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A358" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B358" s="1">
-        <v>260</v>
+        <v>800</v>
       </c>
       <c r="C358" s="1" t="s">
-        <v>279</v>
+        <v>627</v>
       </c>
       <c r="D358" s="3" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A359" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B359" s="1">
-        <v>20</v>
+        <v>830</v>
       </c>
       <c r="C359" s="1" t="s">
-        <v>385</v>
+        <v>628</v>
       </c>
       <c r="D359" s="3" t="s">
-        <v>205</v>
+        <v>20</v>
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A360" s="1" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B360" s="1">
-        <v>87</v>
+        <v>1500</v>
       </c>
       <c r="C360" s="1" t="s">
-        <v>19</v>
+        <v>528</v>
       </c>
       <c r="D360" s="3" t="s">
         <v>20</v>
@@ -19160,58 +19176,58 @@
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A361" s="1" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B361" s="1">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="C361" s="1" t="s">
-        <v>24</v>
+        <v>574</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A362" s="1" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B362" s="1">
-        <v>200</v>
+        <v>390</v>
       </c>
       <c r="C362" s="1" t="s">
-        <v>21</v>
+        <v>280</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A363" s="1" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B363" s="1">
-        <v>25</v>
+        <v>260</v>
       </c>
       <c r="C363" s="1" t="s">
-        <v>23</v>
+        <v>279</v>
       </c>
       <c r="D363" s="3" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A364" s="1" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B364" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C364" s="1" t="s">
-        <v>33</v>
+        <v>385</v>
       </c>
       <c r="D364" s="3" t="s">
-        <v>35</v>
+        <v>205</v>
       </c>
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.45">
@@ -19219,13 +19235,13 @@
         <v>250</v>
       </c>
       <c r="B365" s="1">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="C365" s="1" t="s">
-        <v>383</v>
+        <v>19</v>
       </c>
       <c r="D365" s="3" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.45">
@@ -19233,13 +19249,13 @@
         <v>250</v>
       </c>
       <c r="B366" s="1">
-        <v>32</v>
+        <v>175</v>
       </c>
       <c r="C366" s="1" t="s">
-        <v>458</v>
+        <v>24</v>
       </c>
       <c r="D366" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.45">
@@ -19247,184 +19263,193 @@
         <v>250</v>
       </c>
       <c r="B367" s="1">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="C367" s="1" t="s">
-        <v>460</v>
+        <v>21</v>
       </c>
       <c r="D367" s="3" t="s">
-        <v>368</v>
+        <v>25</v>
       </c>
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A368" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B368" s="1">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>577</v>
+        <v>23</v>
       </c>
       <c r="D368" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A369" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B369" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C369" s="1" t="s">
-        <v>383</v>
+        <v>33</v>
       </c>
       <c r="D369" s="3" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A370" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B370" s="1">
-        <v>5000</v>
+        <v>20</v>
       </c>
       <c r="C370" s="1" t="s">
-        <v>528</v>
+        <v>383</v>
       </c>
       <c r="D370" s="3" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A371" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B371" s="1">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="C371" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D371" s="3" t="s">
-        <v>368</v>
+        <v>42</v>
       </c>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A372" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B372" s="1">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="C372" s="1" t="s">
-        <v>383</v>
+        <v>460</v>
       </c>
       <c r="D372" s="3" t="s">
-        <v>36</v>
+        <v>368</v>
       </c>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A373" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B373" s="1">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C373" s="1" t="s">
-        <v>386</v>
+        <v>575</v>
       </c>
       <c r="D373" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A374" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B374" s="1">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="C374" s="1" t="s">
-        <v>578</v>
+        <v>383</v>
       </c>
       <c r="D374" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A375" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B375" s="1">
+        <v>5000</v>
+      </c>
+      <c r="C375" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="D375" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A376" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B376" s="1">
+        <v>50</v>
+      </c>
+      <c r="C376" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="D376" s="3" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A377" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B377" s="1">
+        <v>20</v>
+      </c>
+      <c r="C377" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D377" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A378" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B378" s="1">
+        <v>80</v>
+      </c>
+      <c r="C378" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D378" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A379" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B379" s="1">
+        <v>150</v>
+      </c>
+      <c r="C379" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="D379" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A380" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B375" s="1">
+      <c r="B380" s="1">
         <f>100+46+100+50</f>
         <v>296</v>
       </c>
-      <c r="C375" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="D375" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A376" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="B376" s="1">
-        <v>80</v>
-      </c>
-      <c r="C376" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="D376" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A377" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="B377" s="1">
-        <v>20</v>
-      </c>
-      <c r="C377" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="D377" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A378" s="1" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A379" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="B379" s="1">
-        <v>100</v>
-      </c>
-      <c r="C379" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D379" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A380" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="B380" s="1">
-        <v>263</v>
-      </c>
       <c r="C380" s="1" t="s">
-        <v>19</v>
+        <v>577</v>
       </c>
       <c r="D380" s="3" t="s">
         <v>20</v>
@@ -19432,44 +19457,35 @@
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A381" s="1" t="s">
-        <v>283</v>
+        <v>255</v>
       </c>
       <c r="B381" s="1">
-        <v>300</v>
+        <v>80</v>
       </c>
       <c r="C381" s="1" t="s">
-        <v>23</v>
+        <v>578</v>
       </c>
       <c r="D381" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A382" s="1" t="s">
-        <v>283</v>
+        <v>255</v>
       </c>
       <c r="B382" s="1">
-        <v>350</v>
+        <v>20</v>
       </c>
       <c r="C382" s="1" t="s">
-        <v>24</v>
+        <v>386</v>
       </c>
       <c r="D382" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A383" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="B383" s="1">
-        <v>30</v>
-      </c>
-      <c r="C383" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D383" s="3" t="s">
-        <v>35</v>
+        <v>282</v>
       </c>
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.45">
@@ -19477,13 +19493,13 @@
         <v>283</v>
       </c>
       <c r="B384" s="1">
-        <v>350</v>
+        <v>100</v>
       </c>
       <c r="C384" s="1" t="s">
-        <v>21</v>
+        <v>284</v>
       </c>
       <c r="D384" s="3" t="s">
-        <v>25</v>
+        <v>188</v>
       </c>
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.45">
@@ -19491,13 +19507,13 @@
         <v>283</v>
       </c>
       <c r="B385" s="1">
-        <v>375</v>
+        <v>263</v>
       </c>
       <c r="C385" s="1" t="s">
-        <v>460</v>
+        <v>19</v>
       </c>
       <c r="D385" s="3" t="s">
-        <v>368</v>
+        <v>20</v>
       </c>
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.45">
@@ -19505,13 +19521,13 @@
         <v>283</v>
       </c>
       <c r="B386" s="1">
-        <v>140</v>
+        <v>300</v>
       </c>
       <c r="C386" s="1" t="s">
-        <v>386</v>
+        <v>23</v>
       </c>
       <c r="D386" s="3" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.45">
@@ -19519,13 +19535,13 @@
         <v>283</v>
       </c>
       <c r="B387" s="1">
-        <v>80</v>
+        <v>350</v>
       </c>
       <c r="C387" s="1" t="s">
-        <v>436</v>
+        <v>24</v>
       </c>
       <c r="D387" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.45">
@@ -19533,13 +19549,13 @@
         <v>283</v>
       </c>
       <c r="B388" s="1">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="C388" s="1" t="s">
-        <v>383</v>
+        <v>33</v>
       </c>
       <c r="D388" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.45">
@@ -19547,13 +19563,13 @@
         <v>283</v>
       </c>
       <c r="B389" s="1">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="C389" s="1" t="s">
-        <v>677</v>
+        <v>21</v>
       </c>
       <c r="D389" s="3" t="s">
-        <v>684</v>
+        <v>25</v>
       </c>
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.45">
@@ -19561,169 +19577,178 @@
         <v>283</v>
       </c>
       <c r="B390" s="1">
-        <v>1500</v>
+        <v>375</v>
       </c>
       <c r="C390" s="1" t="s">
-        <v>676</v>
+        <v>460</v>
       </c>
       <c r="D390" s="3" t="s">
-        <v>683</v>
+        <v>368</v>
       </c>
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A391" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B391" s="1">
-        <v>1684</v>
+        <v>140</v>
       </c>
       <c r="C391" s="1" t="s">
-        <v>581</v>
+        <v>386</v>
       </c>
       <c r="D391" s="3" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A392" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B392" s="1">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="C392" s="1" t="s">
-        <v>383</v>
+        <v>436</v>
       </c>
       <c r="D392" s="3" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A393" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B393" s="1">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="C393" s="1" t="s">
-        <v>678</v>
+        <v>383</v>
       </c>
       <c r="D393" s="3" t="s">
-        <v>684</v>
+        <v>36</v>
       </c>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A394" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B394" s="1">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="C394" s="1" t="s">
-        <v>577</v>
+        <v>675</v>
       </c>
       <c r="D394" s="3" t="s">
-        <v>42</v>
+        <v>682</v>
       </c>
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A395" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B395" s="1">
-        <v>20</v>
+        <v>1500</v>
       </c>
       <c r="C395" s="1" t="s">
-        <v>436</v>
+        <v>674</v>
       </c>
       <c r="D395" s="3" t="s">
-        <v>22</v>
+        <v>681</v>
       </c>
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A396" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B396" s="1">
-        <v>40</v>
+        <v>1684</v>
       </c>
       <c r="C396" s="1" t="s">
-        <v>384</v>
+        <v>579</v>
       </c>
       <c r="D396" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A397" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B397" s="1">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C397" s="1" t="s">
-        <v>262</v>
+        <v>383</v>
       </c>
       <c r="D397" s="3" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A398" s="1" t="s">
-        <v>360</v>
+        <v>285</v>
+      </c>
+      <c r="B398" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C398" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="D398" s="3" t="s">
+        <v>682</v>
       </c>
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A399" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B399" s="1">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="C399" s="1" t="s">
-        <v>679</v>
+        <v>575</v>
       </c>
       <c r="D399" s="3" t="s">
-        <v>684</v>
+        <v>42</v>
       </c>
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A400" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B400" s="1">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="C400" s="1" t="s">
-        <v>460</v>
+        <v>436</v>
       </c>
       <c r="D400" s="3" t="s">
-        <v>368</v>
+        <v>22</v>
       </c>
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A401" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B401" s="1">
-        <v>1500</v>
+        <v>40</v>
       </c>
       <c r="C401" s="1" t="s">
-        <v>58</v>
+        <v>384</v>
       </c>
       <c r="D401" s="3" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A402" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B402" s="1">
-        <v>572</v>
+        <v>60</v>
       </c>
       <c r="C402" s="1" t="s">
-        <v>582</v>
+        <v>262</v>
       </c>
       <c r="D402" s="3" t="s">
         <v>20</v>
@@ -19731,114 +19756,105 @@
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A403" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="B403" s="1">
-        <v>161</v>
-      </c>
-      <c r="C403" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="D403" s="3" t="s">
-        <v>20</v>
+        <v>360</v>
       </c>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A404" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B404" s="1">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="C404" s="1" t="s">
-        <v>584</v>
+        <v>677</v>
       </c>
       <c r="D404" s="3" t="s">
-        <v>362</v>
+        <v>682</v>
       </c>
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A405" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B405" s="1">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="C405" s="1" t="s">
-        <v>238</v>
+        <v>460</v>
       </c>
       <c r="D405" s="3" t="s">
-        <v>684</v>
+        <v>368</v>
       </c>
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A406" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B406" s="1">
-        <v>610</v>
+        <v>1500</v>
       </c>
       <c r="C406" s="1" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="D406" s="3" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A407" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B407" s="1">
-        <v>25</v>
+        <v>572</v>
       </c>
       <c r="C407" s="1" t="s">
-        <v>24</v>
+        <v>580</v>
       </c>
       <c r="D407" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A408" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B408" s="1">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="C408" s="1" t="s">
-        <v>23</v>
+        <v>581</v>
       </c>
       <c r="D408" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A409" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B409" s="1">
         <v>100</v>
       </c>
       <c r="C409" s="1" t="s">
-        <v>21</v>
+        <v>582</v>
       </c>
       <c r="D409" s="3" t="s">
-        <v>25</v>
+        <v>362</v>
       </c>
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A410" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B410" s="1">
-        <v>400</v>
+        <v>25</v>
       </c>
       <c r="C410" s="1" t="s">
-        <v>466</v>
+        <v>238</v>
       </c>
       <c r="D410" s="3" t="s">
-        <v>22</v>
+        <v>682</v>
       </c>
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.45">
@@ -19846,94 +19862,94 @@
         <v>289</v>
       </c>
       <c r="B411" s="1">
-        <v>30</v>
+        <v>610</v>
       </c>
       <c r="C411" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="D411" s="3" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A412" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B412" s="1">
-        <v>225</v>
+        <v>25</v>
       </c>
       <c r="C412" s="1" t="s">
-        <v>465</v>
+        <v>24</v>
       </c>
       <c r="D412" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A413" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B413" s="1">
-        <v>443</v>
+        <v>150</v>
       </c>
       <c r="C413" s="1" t="s">
-        <v>631</v>
+        <v>23</v>
       </c>
       <c r="D413" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A414" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B414" s="1">
-        <v>443</v>
+        <v>100</v>
       </c>
       <c r="C414" s="1" t="s">
-        <v>632</v>
+        <v>21</v>
       </c>
       <c r="D414" s="3" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A415" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B415" s="1">
-        <v>50</v>
+        <v>400</v>
       </c>
       <c r="C415" s="1" t="s">
-        <v>641</v>
+        <v>466</v>
       </c>
       <c r="D415" s="3" t="s">
-        <v>20</v>
+        <v>688</v>
       </c>
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A416" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B416" s="1">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C416" s="1" t="s">
-        <v>383</v>
+        <v>33</v>
       </c>
       <c r="D416" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A417" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B417" s="1">
-        <v>153</v>
+        <v>225</v>
       </c>
       <c r="C417" s="1" t="s">
-        <v>19</v>
+        <v>465</v>
       </c>
       <c r="D417" s="3" t="s">
         <v>20</v>
@@ -19941,30 +19957,30 @@
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A418" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B418" s="1">
-        <v>20</v>
+        <v>443</v>
       </c>
       <c r="C418" s="1" t="s">
-        <v>385</v>
+        <v>629</v>
       </c>
       <c r="D418" s="3" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A419" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B419" s="1">
-        <v>20</v>
+        <v>443</v>
       </c>
       <c r="C419" s="1" t="s">
-        <v>386</v>
+        <v>630</v>
       </c>
       <c r="D419" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.45">
@@ -19975,10 +19991,10 @@
         <v>50</v>
       </c>
       <c r="C420" s="1" t="s">
-        <v>23</v>
+        <v>639</v>
       </c>
       <c r="D420" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.45">
@@ -19986,24 +20002,24 @@
         <v>291</v>
       </c>
       <c r="B421" s="1">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="C421" s="1" t="s">
-        <v>217</v>
+        <v>383</v>
       </c>
       <c r="D421" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A422" s="1" t="s">
-        <v>643</v>
+        <v>291</v>
       </c>
       <c r="B422" s="1">
-        <v>50</v>
+        <v>153</v>
       </c>
       <c r="C422" s="1" t="s">
-        <v>465</v>
+        <v>19</v>
       </c>
       <c r="D422" s="3" t="s">
         <v>20</v>
@@ -20011,13 +20027,13 @@
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A423" s="1" t="s">
-        <v>644</v>
+        <v>291</v>
       </c>
       <c r="B423" s="1">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C423" s="1" t="s">
-        <v>363</v>
+        <v>385</v>
       </c>
       <c r="D423" s="3" t="s">
         <v>41</v>
@@ -20025,84 +20041,84 @@
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A424" s="1" t="s">
-        <v>644</v>
+        <v>291</v>
       </c>
       <c r="B424" s="1">
+        <v>20</v>
+      </c>
+      <c r="C424" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D424" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="425" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A425" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B425" s="1">
+        <v>50</v>
+      </c>
+      <c r="C425" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D425" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="426" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A426" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B426" s="1">
+        <v>25</v>
+      </c>
+      <c r="C426" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D426" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="427" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A427" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="B427" s="1">
+        <v>50</v>
+      </c>
+      <c r="C427" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="D427" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="428" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A428" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="B428" s="1">
+        <v>25</v>
+      </c>
+      <c r="C428" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="D428" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="429" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A429" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="B429" s="1">
         <f>130+55+50</f>
         <v>235</v>
       </c>
-      <c r="C424" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="D424" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A425" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="B425" s="1">
-        <v>75</v>
-      </c>
-      <c r="C425" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="D425" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A426" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="B426" s="1">
-        <v>55</v>
-      </c>
-      <c r="C426" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="D426" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A427" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="B427" s="1">
-        <v>50</v>
-      </c>
-      <c r="C427" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D427" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A428" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="B428" s="1">
-        <v>50</v>
-      </c>
-      <c r="C428" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D428" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A429" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="B429" s="1">
-        <v>1500</v>
-      </c>
       <c r="C429" s="1" t="s">
-        <v>294</v>
+        <v>583</v>
       </c>
       <c r="D429" s="3" t="s">
         <v>20</v>
@@ -20110,405 +20126,405 @@
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A430" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B430" s="1">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="C430" s="1" t="s">
-        <v>386</v>
+        <v>464</v>
       </c>
       <c r="D430" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A431" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B431" s="1">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="C431" s="1" t="s">
-        <v>436</v>
+        <v>217</v>
       </c>
       <c r="D431" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A432" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B432" s="1">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="C432" s="1" t="s">
-        <v>586</v>
+        <v>23</v>
       </c>
       <c r="D432" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A433" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B433" s="1">
+        <v>50</v>
+      </c>
+      <c r="C433" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D433" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="434" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A434" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B434" s="1">
+        <v>1500</v>
+      </c>
+      <c r="C434" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="D434" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="435" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A435" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B435" s="1">
+        <v>60</v>
+      </c>
+      <c r="C435" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D435" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="436" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A436" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B436" s="1">
+        <v>20</v>
+      </c>
+      <c r="C436" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="D436" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="437" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A437" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B433" s="1">
+      <c r="B437" s="1">
+        <v>160</v>
+      </c>
+      <c r="C437" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="D437" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="438" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A438" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B438" s="1">
         <f>75+225</f>
         <v>300</v>
       </c>
-      <c r="C433" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="D433" s="3" t="s">
+      <c r="C438" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="D438" s="3" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="434" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A434" s="1" t="s">
+    <row r="439" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A439" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B434" s="1">
+      <c r="B439" s="1">
         <v>75</v>
       </c>
-      <c r="C434" s="1" t="s">
+      <c r="C439" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="D434" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="435" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A435" s="1" t="s">
+      <c r="D439" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="440" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A440" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B435" s="1">
+      <c r="B440" s="1">
         <v>40</v>
       </c>
-      <c r="C435" s="1" t="s">
+      <c r="C440" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="D435" s="3" t="s">
+      <c r="D440" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="436" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A436" s="1" t="s">
+    <row r="441" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A441" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B436" s="1">
+      <c r="B441" s="1">
         <v>30</v>
       </c>
-      <c r="C436" s="1" t="s">
+      <c r="C441" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="D436" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="437" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A437" s="1" t="s">
+      <c r="D441" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="442" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A442" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B437" s="1">
-        <v>20</v>
-      </c>
-      <c r="C437" s="1" t="s">
+      <c r="B442" s="1">
+        <v>20</v>
+      </c>
+      <c r="C442" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="D437" s="3" t="s">
+      <c r="D442" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="438" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A438" s="1" t="s">
+    <row r="443" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A443" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B438" s="1">
+      <c r="B443" s="1">
         <f>54+50+50</f>
         <v>154</v>
       </c>
-      <c r="C438" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="D438" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="439" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A439" s="1" t="s">
+      <c r="C443" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="D443" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="444" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A444" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B439" s="1">
+      <c r="B444" s="1">
         <v>25</v>
       </c>
-      <c r="C439" s="1" t="s">
+      <c r="C444" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="D439" s="3" t="s">
+      <c r="D444" s="3" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="440" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A440" s="1" t="s">
+    <row r="445" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A445" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B440" s="1">
+      <c r="B445" s="1">
         <v>75</v>
       </c>
-      <c r="C440" s="1" t="s">
-        <v>588</v>
-      </c>
-      <c r="D440" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="441" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A441" s="1" t="s">
+      <c r="C445" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="D445" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="446" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A446" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B441" s="1">
+      <c r="B446" s="1">
         <f>620+100+30</f>
         <v>750</v>
       </c>
-      <c r="C441" s="1" t="s">
+      <c r="C446" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="D441" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="442" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A442" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="B442" s="1">
-        <v>20</v>
-      </c>
-      <c r="C442" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="D442" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="443" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A443" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="B443" s="1">
-        <v>60</v>
-      </c>
-      <c r="C443" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="D443" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="444" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A444" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="B444" s="1">
-        <v>60</v>
-      </c>
-      <c r="C444" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="D444" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="445" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A445" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="B445" s="1">
-        <v>50</v>
-      </c>
-      <c r="C445" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D445" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="446" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A446" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="B446" s="1">
-        <v>25</v>
-      </c>
-      <c r="C446" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="D446" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="447" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A447" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B447" s="1">
+        <v>20</v>
+      </c>
+      <c r="C447" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D447" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="448" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A448" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B448" s="1">
+        <v>60</v>
+      </c>
+      <c r="C448" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="D448" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="449" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A449" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B449" s="1">
+        <v>60</v>
+      </c>
+      <c r="C449" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D449" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A450" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B450" s="1">
+        <v>50</v>
+      </c>
+      <c r="C450" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D450" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A451" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B451" s="1">
+        <v>25</v>
+      </c>
+      <c r="C451" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D451" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="452" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A452" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B447" s="1">
+      <c r="B452" s="1">
         <f>478+180</f>
         <v>658</v>
       </c>
-      <c r="C447" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="D447" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="448" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A448" s="1" t="s">
+      <c r="C452" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="D452" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="453" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A453" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B448" s="1">
+      <c r="B453" s="1">
         <v>325</v>
       </c>
-      <c r="C448" s="1" t="s">
+      <c r="C453" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="D448" s="3" t="s">
+      <c r="D453" s="3" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="449" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A449" s="1" t="s">
+    <row r="454" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A454" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B449" s="1">
+      <c r="B454" s="1">
         <v>140</v>
       </c>
-      <c r="C449" s="1" t="s">
+      <c r="C454" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="D449" s="3" t="s">
+      <c r="D454" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="450" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A450" s="1" t="s">
+    <row r="455" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A455" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B450" s="1">
+      <c r="B455" s="1">
         <f>100+120+620+50</f>
         <v>890</v>
       </c>
-      <c r="C450" s="1" t="s">
+      <c r="C455" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="D450" s="3" t="s">
+      <c r="D455" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="451" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A451" s="1" t="s">
+    <row r="456" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A456" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B451" s="1">
+      <c r="B456" s="1">
         <v>50</v>
       </c>
-      <c r="C451" s="1" t="s">
+      <c r="C456" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="D451" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="452" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A452" s="1" t="s">
+      <c r="D456" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="457" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A457" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B452" s="1">
+      <c r="B457" s="1">
         <f>243+100+30</f>
         <v>373</v>
       </c>
-      <c r="C452" s="1" t="s">
+      <c r="C457" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="D452" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="453" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A453" s="1" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="454" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A454" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B454" s="1">
-        <v>90</v>
-      </c>
-      <c r="C454" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D454" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="455" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A455" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B455" s="1">
-        <v>25</v>
-      </c>
-      <c r="C455" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D455" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="456" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A456" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B456" s="1">
-        <v>20</v>
-      </c>
-      <c r="C456" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="D456" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="457" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A457" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B457" s="1">
-        <v>50</v>
-      </c>
-      <c r="C457" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="D457" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="458" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A458" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B458" s="1">
-        <v>25</v>
-      </c>
-      <c r="C458" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="D458" s="3" t="s">
-        <v>684</v>
+        <v>307</v>
       </c>
     </row>
     <row r="459" spans="1:4" x14ac:dyDescent="0.45">
@@ -20516,13 +20532,13 @@
         <v>11</v>
       </c>
       <c r="B459" s="1">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="C459" s="1" t="s">
-        <v>308</v>
+        <v>78</v>
       </c>
       <c r="D459" s="3" t="s">
-        <v>686</v>
+        <v>35</v>
       </c>
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.45">
@@ -20530,10 +20546,10 @@
         <v>11</v>
       </c>
       <c r="B460" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="C460" s="1" t="s">
-        <v>470</v>
+        <v>90</v>
       </c>
       <c r="D460" s="3" t="s">
         <v>22</v>
@@ -20541,83 +20557,83 @@
     </row>
     <row r="461" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A461" s="1" t="s">
-        <v>309</v>
+        <v>11</v>
       </c>
       <c r="B461" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="C461" s="1" t="s">
-        <v>465</v>
+        <v>386</v>
       </c>
       <c r="D461" s="3" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
     </row>
     <row r="462" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A462" s="1" t="s">
-        <v>310</v>
+        <v>11</v>
       </c>
       <c r="B462" s="1">
         <v>50</v>
       </c>
       <c r="C462" s="1" t="s">
-        <v>364</v>
+        <v>23</v>
       </c>
       <c r="D462" s="3" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="463" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A463" s="1" t="s">
-        <v>310</v>
+        <v>11</v>
       </c>
       <c r="B463" s="1">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C463" s="1" t="s">
-        <v>471</v>
+        <v>238</v>
       </c>
       <c r="D463" s="3" t="s">
-        <v>36</v>
+        <v>682</v>
       </c>
     </row>
     <row r="464" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A464" s="1" t="s">
-        <v>310</v>
+        <v>11</v>
       </c>
       <c r="B464" s="1">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="C464" s="1" t="s">
-        <v>109</v>
+        <v>308</v>
       </c>
       <c r="D464" s="3" t="s">
-        <v>22</v>
+        <v>684</v>
       </c>
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A465" s="1" t="s">
-        <v>311</v>
+        <v>11</v>
       </c>
       <c r="B465" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C465" s="1" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="D465" s="3" t="s">
-        <v>20</v>
+        <v>688</v>
       </c>
     </row>
     <row r="466" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A466" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B466" s="1">
-        <v>155</v>
+        <v>100</v>
       </c>
       <c r="C466" s="1" t="s">
-        <v>19</v>
+        <v>465</v>
       </c>
       <c r="D466" s="3" t="s">
         <v>20</v>
@@ -20625,171 +20641,171 @@
     </row>
     <row r="467" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A467" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B467" s="1">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="C467" s="1" t="s">
-        <v>90</v>
+        <v>364</v>
       </c>
       <c r="D467" s="3" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
     </row>
     <row r="468" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A468" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B468" s="1">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="C468" s="1" t="s">
-        <v>313</v>
+        <v>471</v>
       </c>
       <c r="D468" s="3" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A469" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B469" s="1">
+        <v>50</v>
+      </c>
+      <c r="C469" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D469" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="470" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A470" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B470" s="1">
+        <v>50</v>
+      </c>
+      <c r="C470" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="D470" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="471" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A471" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B471" s="1">
+        <v>155</v>
+      </c>
+      <c r="C471" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D471" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="472" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A472" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B472" s="1">
+        <v>25</v>
+      </c>
+      <c r="C472" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D472" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="473" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A473" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B469" s="1">
+      <c r="B473" s="1">
+        <v>75</v>
+      </c>
+      <c r="C473" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="D473" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="474" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A474" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B474" s="1">
         <f>75+50</f>
         <v>125</v>
       </c>
-      <c r="C469" s="1" t="s">
+      <c r="C474" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="D469" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="470" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A470" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="B470" s="1">
-        <v>500</v>
-      </c>
-      <c r="C470" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="D470" s="3" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="471" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A471" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="B471" s="1">
-        <v>40</v>
-      </c>
-      <c r="C471" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D471" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="472" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A472" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="B472" s="1">
-        <v>75</v>
-      </c>
-      <c r="C472" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D472" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="473" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A473" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B473" s="1">
-        <v>447</v>
-      </c>
-      <c r="C473" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="D473" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="474" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A474" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B474" s="1">
-        <v>25</v>
-      </c>
-      <c r="C474" s="1" t="s">
-        <v>316</v>
-      </c>
       <c r="D474" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="475" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A475" s="1" t="s">
-        <v>12</v>
+        <v>312</v>
       </c>
       <c r="B475" s="1">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="C475" s="1" t="s">
-        <v>474</v>
+        <v>678</v>
       </c>
       <c r="D475" s="3" t="s">
-        <v>362</v>
+        <v>682</v>
       </c>
     </row>
     <row r="476" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A476" s="1" t="s">
-        <v>12</v>
+        <v>314</v>
       </c>
       <c r="B476" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C476" s="1" t="s">
-        <v>436</v>
+        <v>387</v>
       </c>
       <c r="D476" s="3" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
     </row>
     <row r="477" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A477" s="1" t="s">
-        <v>12</v>
+        <v>314</v>
       </c>
       <c r="B477" s="1">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="C477" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D477" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A478" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B478" s="1">
-        <v>150</v>
+        <v>447</v>
       </c>
       <c r="C478" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D478" s="3" t="s">
-        <v>273</v>
+        <v>20</v>
       </c>
     </row>
     <row r="479" spans="1:4" x14ac:dyDescent="0.45">
@@ -20797,13 +20813,13 @@
         <v>12</v>
       </c>
       <c r="B479" s="1">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="C479" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="D479" s="3" t="s">
-        <v>270</v>
+        <v>26</v>
       </c>
     </row>
     <row r="480" spans="1:4" x14ac:dyDescent="0.45">
@@ -20811,32 +20827,32 @@
         <v>12</v>
       </c>
       <c r="B480" s="1">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="C480" s="1" t="s">
-        <v>318</v>
+        <v>474</v>
       </c>
       <c r="D480" s="3" t="s">
-        <v>269</v>
+        <v>362</v>
       </c>
     </row>
     <row r="481" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A481" s="1" t="s">
-        <v>319</v>
+        <v>12</v>
       </c>
       <c r="B481" s="1">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="C481" s="1" t="s">
-        <v>464</v>
+        <v>436</v>
       </c>
       <c r="D481" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="482" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A482" s="1" t="s">
-        <v>319</v>
+        <v>12</v>
       </c>
       <c r="B482" s="1">
         <v>100</v>
@@ -20845,127 +20861,127 @@
         <v>21</v>
       </c>
       <c r="D482" s="3" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="483" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A483" s="1" t="s">
-        <v>320</v>
+        <v>12</v>
       </c>
       <c r="B483" s="1">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="C483" s="1" t="s">
-        <v>24</v>
+        <v>317</v>
       </c>
       <c r="D483" s="3" t="s">
-        <v>20</v>
+        <v>273</v>
       </c>
     </row>
     <row r="484" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A484" s="1" t="s">
-        <v>320</v>
+        <v>12</v>
       </c>
       <c r="B484" s="1">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C484" s="1" t="s">
-        <v>463</v>
+        <v>313</v>
       </c>
       <c r="D484" s="3" t="s">
-        <v>22</v>
+        <v>270</v>
       </c>
     </row>
     <row r="485" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A485" s="1" t="s">
-        <v>320</v>
+        <v>12</v>
       </c>
       <c r="B485" s="1">
         <v>25</v>
       </c>
       <c r="C485" s="1" t="s">
-        <v>90</v>
+        <v>318</v>
       </c>
       <c r="D485" s="3" t="s">
-        <v>22</v>
+        <v>269</v>
       </c>
     </row>
     <row r="486" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A486" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B486" s="1">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="C486" s="1" t="s">
-        <v>386</v>
+        <v>464</v>
       </c>
       <c r="D486" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
     </row>
     <row r="487" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A487" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B487" s="1">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="C487" s="1" t="s">
-        <v>383</v>
+        <v>21</v>
       </c>
       <c r="D487" s="3" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="488" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A488" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B488" s="1">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="C488" s="1" t="s">
-        <v>475</v>
+        <v>24</v>
       </c>
       <c r="D488" s="3" t="s">
-        <v>362</v>
+        <v>20</v>
       </c>
     </row>
     <row r="489" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A489" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B489" s="1">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="C489" s="1" t="s">
-        <v>476</v>
+        <v>463</v>
       </c>
       <c r="D489" s="3" t="s">
-        <v>365</v>
+        <v>22</v>
       </c>
     </row>
     <row r="490" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A490" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B490" s="1">
         <v>25</v>
       </c>
       <c r="C490" s="1" t="s">
-        <v>477</v>
+        <v>90</v>
       </c>
       <c r="D490" s="3" t="s">
-        <v>366</v>
+        <v>22</v>
       </c>
     </row>
     <row r="491" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A491" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B491" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C491" s="1" t="s">
         <v>386</v>
@@ -20976,58 +20992,58 @@
     </row>
     <row r="492" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A492" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B492" s="1">
-        <v>201</v>
+        <v>20</v>
       </c>
       <c r="C492" s="1" t="s">
-        <v>19</v>
+        <v>383</v>
       </c>
       <c r="D492" s="3" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
     </row>
     <row r="493" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A493" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B493" s="1">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="C493" s="1" t="s">
-        <v>24</v>
+        <v>475</v>
       </c>
       <c r="D493" s="3" t="s">
-        <v>27</v>
+        <v>362</v>
       </c>
     </row>
     <row r="494" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A494" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B494" s="1">
-        <v>1100</v>
+        <v>25</v>
       </c>
       <c r="C494" s="1" t="s">
-        <v>615</v>
+        <v>476</v>
       </c>
       <c r="D494" s="3" t="s">
-        <v>20</v>
+        <v>365</v>
       </c>
     </row>
     <row r="495" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A495" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B495" s="1">
-        <v>900</v>
+        <v>25</v>
       </c>
       <c r="C495" s="1" t="s">
-        <v>616</v>
+        <v>477</v>
       </c>
       <c r="D495" s="3" t="s">
-        <v>20</v>
+        <v>366</v>
       </c>
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.45">
@@ -21035,13 +21051,13 @@
         <v>322</v>
       </c>
       <c r="B496" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C496" s="1" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D496" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="497" spans="1:4" x14ac:dyDescent="0.45">
@@ -21049,13 +21065,13 @@
         <v>322</v>
       </c>
       <c r="B497" s="1">
-        <v>20</v>
+        <v>201</v>
       </c>
       <c r="C497" s="1" t="s">
-        <v>478</v>
+        <v>19</v>
       </c>
       <c r="D497" s="3" t="s">
-        <v>367</v>
+        <v>20</v>
       </c>
     </row>
     <row r="498" spans="1:4" x14ac:dyDescent="0.45">
@@ -21063,88 +21079,88 @@
         <v>322</v>
       </c>
       <c r="B498" s="1">
-        <v>291</v>
+        <v>50</v>
       </c>
       <c r="C498" s="1" t="s">
-        <v>323</v>
+        <v>24</v>
       </c>
       <c r="D498" s="3" t="s">
-        <v>367</v>
+        <v>27</v>
       </c>
     </row>
     <row r="499" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A499" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
+      </c>
+      <c r="B499" s="1">
+        <v>1100</v>
+      </c>
+      <c r="C499" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="D499" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="500" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A500" s="1" t="s">
-        <v>9</v>
+        <v>322</v>
       </c>
       <c r="B500" s="1">
-        <v>250</v>
+        <v>900</v>
       </c>
       <c r="C500" s="1" t="s">
-        <v>21</v>
+        <v>614</v>
       </c>
       <c r="D500" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="501" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A501" s="1" t="s">
-        <v>9</v>
+        <v>322</v>
       </c>
       <c r="B501" s="1">
-        <v>275</v>
+        <v>20</v>
       </c>
       <c r="C501" s="1" t="s">
-        <v>24</v>
+        <v>383</v>
       </c>
       <c r="D501" s="3" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
     </row>
     <row r="502" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A502" s="1" t="s">
-        <v>9</v>
+        <v>322</v>
       </c>
       <c r="B502" s="1">
-        <v>115</v>
+        <v>20</v>
       </c>
       <c r="C502" s="1" t="s">
-        <v>33</v>
+        <v>478</v>
       </c>
       <c r="D502" s="3" t="s">
-        <v>35</v>
+        <v>367</v>
       </c>
     </row>
     <row r="503" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A503" s="1" t="s">
-        <v>9</v>
+        <v>322</v>
       </c>
       <c r="B503" s="1">
-        <v>75</v>
+        <v>291</v>
       </c>
       <c r="C503" s="1" t="s">
-        <v>390</v>
+        <v>323</v>
       </c>
       <c r="D503" s="3" t="s">
-        <v>42</v>
+        <v>367</v>
       </c>
     </row>
     <row r="504" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A504" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B504" s="1">
-        <v>60</v>
-      </c>
-      <c r="C504" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="D504" s="3" t="s">
-        <v>374</v>
+        <v>324</v>
       </c>
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.45">
@@ -21152,13 +21168,13 @@
         <v>9</v>
       </c>
       <c r="B505" s="1">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="C505" s="1" t="s">
-        <v>590</v>
+        <v>21</v>
       </c>
       <c r="D505" s="3" t="s">
-        <v>368</v>
+        <v>25</v>
       </c>
     </row>
     <row r="506" spans="1:4" x14ac:dyDescent="0.45">
@@ -21166,13 +21182,13 @@
         <v>9</v>
       </c>
       <c r="B506" s="1">
-        <v>100</v>
+        <v>275</v>
       </c>
       <c r="C506" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D506" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="507" spans="1:4" x14ac:dyDescent="0.45">
@@ -21180,123 +21196,122 @@
         <v>9</v>
       </c>
       <c r="B507" s="1">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="C507" s="1" t="s">
-        <v>532</v>
+        <v>33</v>
       </c>
       <c r="D507" s="3" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
     </row>
     <row r="508" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A508" s="1" t="s">
-        <v>645</v>
+        <v>9</v>
       </c>
       <c r="B508" s="1">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="C508" s="1" t="s">
-        <v>481</v>
+        <v>390</v>
       </c>
       <c r="D508" s="3" t="s">
-        <v>368</v>
+        <v>42</v>
       </c>
     </row>
     <row r="509" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A509" s="1" t="s">
-        <v>645</v>
+        <v>9</v>
       </c>
       <c r="B509" s="1">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="C509" s="1" t="s">
-        <v>23</v>
+        <v>479</v>
       </c>
       <c r="D509" s="3" t="s">
-        <v>26</v>
+        <v>374</v>
       </c>
     </row>
     <row r="510" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A510" s="1" t="s">
-        <v>646</v>
+        <v>9</v>
       </c>
       <c r="B510" s="1">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="C510" s="1" t="s">
-        <v>541</v>
+        <v>588</v>
       </c>
       <c r="D510" s="3" t="s">
-        <v>20</v>
+        <v>368</v>
       </c>
     </row>
     <row r="511" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A511" s="1" t="s">
-        <v>646</v>
+        <v>9</v>
       </c>
       <c r="B511" s="1">
-        <v>215</v>
+        <v>100</v>
       </c>
       <c r="C511" s="1" t="s">
-        <v>647</v>
+        <v>23</v>
       </c>
       <c r="D511" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="512" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A512" s="1" t="s">
-        <v>646</v>
+        <v>9</v>
       </c>
       <c r="B512" s="1">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="C512" s="1" t="s">
-        <v>21</v>
+        <v>532</v>
       </c>
       <c r="D512" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="513" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A513" s="1" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="B513" s="1">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C513" s="1" t="s">
-        <v>33</v>
+        <v>481</v>
       </c>
       <c r="D513" s="3" t="s">
-        <v>35</v>
+        <v>368</v>
       </c>
     </row>
     <row r="514" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A514" s="1" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="B514" s="1">
-        <v>350</v>
+        <v>25</v>
       </c>
       <c r="C514" s="1" t="s">
-        <v>326</v>
+        <v>23</v>
       </c>
       <c r="D514" s="3" t="s">
-        <v>361</v>
+        <v>26</v>
       </c>
     </row>
     <row r="515" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A515" s="1" t="s">
-        <v>327</v>
+        <v>644</v>
       </c>
       <c r="B515" s="1">
-        <f>200+225+30+75</f>
-        <v>530</v>
+        <v>175</v>
       </c>
       <c r="C515" s="1" t="s">
-        <v>591</v>
+        <v>541</v>
       </c>
       <c r="D515" s="3" t="s">
         <v>20</v>
@@ -21304,58 +21319,58 @@
     </row>
     <row r="516" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A516" s="1" t="s">
-        <v>327</v>
+        <v>644</v>
       </c>
       <c r="B516" s="1">
-        <v>1500</v>
+        <v>215</v>
       </c>
       <c r="C516" s="1" t="s">
-        <v>681</v>
+        <v>645</v>
       </c>
       <c r="D516" s="3" t="s">
-        <v>684</v>
+        <v>20</v>
       </c>
     </row>
     <row r="517" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A517" s="1" t="s">
-        <v>327</v>
+        <v>644</v>
       </c>
       <c r="B517" s="1">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="C517" s="1" t="s">
-        <v>481</v>
+        <v>21</v>
       </c>
       <c r="D517" s="3" t="s">
-        <v>369</v>
+        <v>25</v>
       </c>
     </row>
     <row r="518" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A518" s="1" t="s">
-        <v>327</v>
+        <v>644</v>
       </c>
       <c r="B518" s="1">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="C518" s="1" t="s">
-        <v>482</v>
+        <v>33</v>
       </c>
       <c r="D518" s="3" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="519" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A519" s="1" t="s">
-        <v>327</v>
+        <v>644</v>
       </c>
       <c r="B519" s="1">
-        <v>20</v>
+        <v>350</v>
       </c>
       <c r="C519" s="1" t="s">
-        <v>483</v>
+        <v>326</v>
       </c>
       <c r="D519" s="3" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
     </row>
     <row r="520" spans="1:4" x14ac:dyDescent="0.45">
@@ -21363,123 +21378,124 @@
         <v>327</v>
       </c>
       <c r="B520" s="1">
-        <v>50</v>
+        <f>200+225+30+75</f>
+        <v>530</v>
       </c>
       <c r="C520" s="1" t="s">
-        <v>328</v>
+        <v>589</v>
       </c>
       <c r="D520" s="3" t="s">
-        <v>371</v>
+        <v>20</v>
       </c>
     </row>
     <row r="521" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A521" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B521" s="1">
-        <v>75</v>
+        <v>1500</v>
       </c>
       <c r="C521" s="1" t="s">
-        <v>484</v>
+        <v>679</v>
       </c>
       <c r="D521" s="3" t="s">
-        <v>20</v>
+        <v>682</v>
       </c>
     </row>
     <row r="522" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A522" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B522" s="1">
+        <v>20</v>
+      </c>
+      <c r="C522" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="D522" s="3" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="523" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A523" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B523" s="1">
+        <v>20</v>
+      </c>
+      <c r="C523" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="D523" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="524" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A524" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B524" s="1">
+        <v>20</v>
+      </c>
+      <c r="C524" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="D524" s="3" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="525" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A525" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B525" s="1">
+        <v>50</v>
+      </c>
+      <c r="C525" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="D525" s="3" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="526" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A526" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B522" s="1">
+      <c r="B526" s="1">
+        <v>75</v>
+      </c>
+      <c r="C526" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="D526" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="527" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A527" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B527" s="1">
         <f>75+50+100+60</f>
         <v>285</v>
       </c>
-      <c r="C522" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="D522" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="523" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A523" s="1" t="s">
-        <v>636</v>
-      </c>
-      <c r="B523" s="1">
-        <v>490</v>
-      </c>
-      <c r="C523" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="D523" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="524" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A524" s="1" t="s">
-        <v>636</v>
-      </c>
-      <c r="B524" s="1">
-        <v>5240</v>
-      </c>
-      <c r="C524" s="1" t="s">
-        <v>623</v>
-      </c>
-      <c r="D524" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="525" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A525" s="1" t="s">
-        <v>636</v>
-      </c>
-      <c r="B525" s="1">
-        <v>6980</v>
-      </c>
-      <c r="C525" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="D525" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="526" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A526" s="1" t="s">
-        <v>636</v>
-      </c>
-      <c r="B526" s="1">
-        <v>40</v>
-      </c>
-      <c r="C526" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="D526" s="3" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="527" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A527" s="1" t="s">
-        <v>636</v>
-      </c>
-      <c r="B527" s="1">
-        <v>195</v>
-      </c>
       <c r="C527" s="1" t="s">
-        <v>638</v>
+        <v>590</v>
       </c>
       <c r="D527" s="3" t="s">
-        <v>368</v>
+        <v>20</v>
       </c>
     </row>
     <row r="528" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A528" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B528" s="1">
-        <v>50</v>
+        <v>490</v>
       </c>
       <c r="C528" s="1" t="s">
-        <v>24</v>
+        <v>591</v>
       </c>
       <c r="D528" s="3" t="s">
         <v>20</v>
@@ -21487,13 +21503,13 @@
     </row>
     <row r="529" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A529" s="1" t="s">
-        <v>331</v>
+        <v>634</v>
       </c>
       <c r="B529" s="1">
-        <v>105</v>
+        <v>5240</v>
       </c>
       <c r="C529" s="1" t="s">
-        <v>594</v>
+        <v>621</v>
       </c>
       <c r="D529" s="3" t="s">
         <v>20</v>
@@ -21501,87 +21517,86 @@
     </row>
     <row r="530" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A530" s="1" t="s">
-        <v>331</v>
+        <v>634</v>
       </c>
       <c r="B530" s="1">
-        <v>1500</v>
+        <v>6980</v>
       </c>
       <c r="C530" s="1" t="s">
-        <v>682</v>
+        <v>622</v>
       </c>
       <c r="D530" s="3" t="s">
-        <v>687</v>
+        <v>20</v>
       </c>
     </row>
     <row r="531" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A531" s="1" t="s">
-        <v>332</v>
+        <v>634</v>
       </c>
       <c r="B531" s="1">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="C531" s="1" t="s">
-        <v>333</v>
+        <v>485</v>
       </c>
       <c r="D531" s="3" t="s">
-        <v>20</v>
+        <v>377</v>
       </c>
     </row>
     <row r="532" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A532" s="1" t="s">
-        <v>332</v>
+        <v>634</v>
       </c>
       <c r="B532" s="1">
-        <v>60</v>
+        <v>195</v>
       </c>
       <c r="C532" s="1" t="s">
-        <v>650</v>
+        <v>636</v>
       </c>
       <c r="D532" s="3" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
     </row>
     <row r="533" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A533" s="1" t="s">
-        <v>332</v>
+        <v>633</v>
       </c>
       <c r="B533" s="1">
-        <f>90+75</f>
-        <v>165</v>
+        <v>50</v>
       </c>
       <c r="C533" s="1" t="s">
-        <v>651</v>
+        <v>24</v>
       </c>
       <c r="D533" s="3" t="s">
-        <v>368</v>
+        <v>20</v>
       </c>
     </row>
     <row r="534" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A534" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B534" s="1">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="C534" s="1" t="s">
-        <v>485</v>
+        <v>592</v>
       </c>
       <c r="D534" s="3" t="s">
-        <v>377</v>
+        <v>20</v>
       </c>
     </row>
     <row r="535" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A535" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B535" s="1">
-        <v>75</v>
+        <v>1500</v>
       </c>
       <c r="C535" s="1" t="s">
-        <v>390</v>
+        <v>680</v>
       </c>
       <c r="D535" s="3" t="s">
-        <v>42</v>
+        <v>685</v>
       </c>
     </row>
     <row r="536" spans="1:4" x14ac:dyDescent="0.45">
@@ -21589,114 +21604,123 @@
         <v>332</v>
       </c>
       <c r="B536" s="1">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="C536" s="1" t="s">
-        <v>223</v>
+        <v>333</v>
       </c>
       <c r="D536" s="3" t="s">
-        <v>370</v>
+        <v>20</v>
       </c>
     </row>
     <row r="537" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A537" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B537" s="1">
+        <v>60</v>
+      </c>
+      <c r="C537" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="B537" s="1">
-        <v>95</v>
-      </c>
-      <c r="C537" s="1" t="s">
-        <v>649</v>
-      </c>
       <c r="D537" s="3" t="s">
-        <v>20</v>
+        <v>374</v>
       </c>
     </row>
     <row r="538" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A538" s="1" t="s">
-        <v>648</v>
+        <v>332</v>
       </c>
       <c r="B538" s="1">
-        <v>20</v>
+        <f>90+75</f>
+        <v>165</v>
       </c>
       <c r="C538" s="1" t="s">
-        <v>485</v>
+        <v>649</v>
       </c>
       <c r="D538" s="3" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
     </row>
     <row r="539" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A539" s="1" t="s">
-        <v>648</v>
+        <v>332</v>
       </c>
       <c r="B539" s="1">
-        <v>175</v>
+        <v>20</v>
       </c>
       <c r="C539" s="1" t="s">
-        <v>595</v>
+        <v>485</v>
       </c>
       <c r="D539" s="3" t="s">
-        <v>20</v>
+        <v>377</v>
       </c>
     </row>
     <row r="540" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A540" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B540" s="1">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="C540" s="1" t="s">
-        <v>596</v>
+        <v>390</v>
       </c>
       <c r="D540" s="3" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
     </row>
     <row r="541" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A541" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B541" s="1">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C541" s="1" t="s">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="D541" s="3" t="s">
-        <v>20</v>
+        <v>370</v>
       </c>
     </row>
     <row r="542" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A542" s="1" t="s">
-        <v>335</v>
+        <v>646</v>
+      </c>
+      <c r="B542" s="1">
+        <v>95</v>
+      </c>
+      <c r="C542" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="D542" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="543" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A543" s="1" t="s">
-        <v>10</v>
+        <v>646</v>
       </c>
       <c r="B543" s="1">
-        <f>225+475+150+18</f>
-        <v>868</v>
+        <v>20</v>
       </c>
       <c r="C543" s="1" t="s">
-        <v>597</v>
+        <v>485</v>
       </c>
       <c r="D543" s="3" t="s">
-        <v>20</v>
+        <v>377</v>
       </c>
     </row>
     <row r="544" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A544" s="1" t="s">
-        <v>10</v>
+        <v>646</v>
       </c>
       <c r="B544" s="1">
-        <v>80</v>
+        <v>175</v>
       </c>
       <c r="C544" s="1" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="D544" s="3" t="s">
         <v>20</v>
@@ -21704,111 +21728,103 @@
     </row>
     <row r="545" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A545" s="1" t="s">
-        <v>10</v>
+        <v>334</v>
       </c>
       <c r="B545" s="1">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="C545" s="1" t="s">
-        <v>485</v>
+        <v>594</v>
       </c>
       <c r="D545" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="546" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A546" s="1" t="s">
-        <v>10</v>
+        <v>334</v>
       </c>
       <c r="B546" s="1">
-        <v>55</v>
+        <f>260+16</f>
+        <v>276</v>
       </c>
       <c r="C546" s="1" t="s">
-        <v>533</v>
+        <v>595</v>
       </c>
       <c r="D546" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="547" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A547" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="B547" s="1">
-        <v>20</v>
-      </c>
-      <c r="C547" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="D547" s="3" t="s">
-        <v>377</v>
+        <v>335</v>
       </c>
     </row>
     <row r="548" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A548" s="1" t="s">
-        <v>338</v>
+        <v>10</v>
       </c>
       <c r="B548" s="1">
-        <v>60</v>
+        <v>608</v>
       </c>
       <c r="C548" s="1" t="s">
-        <v>534</v>
+        <v>595</v>
       </c>
       <c r="D548" s="3" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="549" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A549" s="1" t="s">
-        <v>338</v>
+        <v>10</v>
       </c>
       <c r="B549" s="1">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="C549" s="1" t="s">
-        <v>341</v>
+        <v>596</v>
       </c>
       <c r="D549" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A550" s="1" t="s">
-        <v>338</v>
+        <v>10</v>
       </c>
       <c r="B550" s="1">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="C550" s="1" t="s">
-        <v>599</v>
+        <v>485</v>
       </c>
       <c r="D550" s="3" t="s">
-        <v>368</v>
+        <v>22</v>
       </c>
     </row>
     <row r="551" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A551" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B551" s="1">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="C551" s="1" t="s">
-        <v>492</v>
+        <v>533</v>
       </c>
       <c r="D551" s="3" t="s">
-        <v>374</v>
+        <v>22</v>
       </c>
     </row>
     <row r="552" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A552" s="1" t="s">
-        <v>13</v>
+        <v>338</v>
       </c>
       <c r="B552" s="1">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C552" s="1" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D552" s="3" t="s">
         <v>377</v>
@@ -21816,86 +21832,86 @@
     </row>
     <row r="553" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A553" s="1" t="s">
-        <v>13</v>
+        <v>338</v>
       </c>
       <c r="B553" s="1">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="C553" s="1" t="s">
-        <v>481</v>
+        <v>534</v>
       </c>
       <c r="D553" s="3" t="s">
-        <v>368</v>
+        <v>35</v>
       </c>
     </row>
     <row r="554" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A554" s="1" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="B554" s="1">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C554" s="1" t="s">
-        <v>600</v>
+        <v>341</v>
       </c>
       <c r="D554" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="555" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A555" s="1" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="B555" s="1">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="C555" s="1" t="s">
-        <v>103</v>
+        <v>597</v>
       </c>
       <c r="D555" s="3" t="s">
-        <v>20</v>
+        <v>368</v>
       </c>
     </row>
     <row r="556" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A556" s="1" t="s">
-        <v>342</v>
+        <v>13</v>
       </c>
       <c r="B556" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C556" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D556" s="3" t="s">
-        <v>22</v>
+        <v>374</v>
       </c>
     </row>
     <row r="557" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A557" s="1" t="s">
-        <v>342</v>
+        <v>13</v>
       </c>
       <c r="B557" s="1">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="C557" s="1" t="s">
-        <v>343</v>
+        <v>485</v>
       </c>
       <c r="D557" s="3" t="s">
-        <v>201</v>
+        <v>377</v>
       </c>
     </row>
     <row r="558" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A558" s="1" t="s">
-        <v>342</v>
+        <v>13</v>
       </c>
       <c r="B558" s="1">
         <v>20</v>
       </c>
       <c r="C558" s="1" t="s">
-        <v>494</v>
+        <v>481</v>
       </c>
       <c r="D558" s="3" t="s">
-        <v>201</v>
+        <v>368</v>
       </c>
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.45">
@@ -21906,120 +21922,120 @@
         <v>60</v>
       </c>
       <c r="C559" s="1" t="s">
-        <v>344</v>
+        <v>598</v>
       </c>
       <c r="D559" s="3" t="s">
-        <v>195</v>
+        <v>20</v>
       </c>
     </row>
     <row r="560" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A560" s="1" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B560" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="C560" s="1" t="s">
-        <v>485</v>
+        <v>103</v>
       </c>
       <c r="D560" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="561" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A561" s="1" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B561" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C561" s="1" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="D561" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="562" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A562" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B562" s="1">
+        <v>75</v>
+      </c>
+      <c r="C562" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="D562" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="563" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A563" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B563" s="1">
+        <v>20</v>
+      </c>
+      <c r="C563" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="D563" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="564" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A564" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B564" s="1">
+        <v>60</v>
+      </c>
+      <c r="C564" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D564" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="565" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A565" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B565" s="1">
+        <v>100</v>
+      </c>
+      <c r="C565" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="D565" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="566" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A566" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B566" s="1">
+        <v>40</v>
+      </c>
+      <c r="C566" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="D566" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="567" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A567" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="B562" s="1">
+      <c r="B567" s="1">
         <f>50+75+30</f>
         <v>155</v>
       </c>
-      <c r="C562" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="D562" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="563" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A563" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="B563" s="1">
-        <v>40</v>
-      </c>
-      <c r="C563" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="D563" s="3" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="564" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A564" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="B564" s="1">
-        <v>60</v>
-      </c>
-      <c r="C564" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="D564" s="3" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="565" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A565" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="B565" s="1">
-        <v>40</v>
-      </c>
-      <c r="C565" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="D565" s="3" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="566" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A566" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="B566" s="1">
-        <v>80</v>
-      </c>
-      <c r="C566" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="D566" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="567" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A567" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="B567" s="1">
-        <v>50</v>
-      </c>
       <c r="C567" s="1" t="s">
-        <v>24</v>
+        <v>599</v>
       </c>
       <c r="D567" s="3" t="s">
         <v>20</v>
@@ -22027,84 +22043,83 @@
     </row>
     <row r="568" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A568" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B568" s="1">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C568" s="1" t="s">
-        <v>33</v>
+        <v>492</v>
       </c>
       <c r="D568" s="3" t="s">
-        <v>35</v>
+        <v>374</v>
       </c>
     </row>
     <row r="569" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A569" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B569" s="1">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="C569" s="1" t="s">
-        <v>496</v>
+        <v>482</v>
       </c>
       <c r="D569" s="3" t="s">
-        <v>35</v>
+        <v>374</v>
       </c>
     </row>
     <row r="570" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A570" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B570" s="1">
         <v>40</v>
       </c>
       <c r="C570" s="1" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="D570" s="3" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
     </row>
     <row r="571" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A571" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B571" s="1">
-        <v>300</v>
+        <v>80</v>
       </c>
       <c r="C571" s="1" t="s">
-        <v>24</v>
+        <v>596</v>
       </c>
       <c r="D571" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="572" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A572" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B572" s="1">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="C572" s="1" t="s">
-        <v>497</v>
+        <v>24</v>
       </c>
       <c r="D572" s="3" t="s">
-        <v>377</v>
+        <v>20</v>
       </c>
     </row>
     <row r="573" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A573" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B573" s="1">
-        <f>285+60</f>
-        <v>345</v>
+        <v>30</v>
       </c>
       <c r="C573" s="1" t="s">
-        <v>602</v>
+        <v>33</v>
       </c>
       <c r="D573" s="3" t="s">
         <v>35</v>
@@ -22112,16 +22127,16 @@
     </row>
     <row r="574" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A574" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B574" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C574" s="1" t="s">
-        <v>354</v>
+        <v>496</v>
       </c>
       <c r="D574" s="3" t="s">
-        <v>199</v>
+        <v>35</v>
       </c>
     </row>
     <row r="575" spans="1:4" x14ac:dyDescent="0.45">
@@ -22132,49 +22147,50 @@
         <v>40</v>
       </c>
       <c r="C575" s="1" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="D575" s="3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="576" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A576" s="1" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="B576" s="1">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="C576" s="1" t="s">
-        <v>655</v>
+        <v>24</v>
       </c>
       <c r="D576" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="577" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A577" s="1" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="B577" s="1">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C577" s="1" t="s">
-        <v>24</v>
+        <v>497</v>
       </c>
       <c r="D577" s="3" t="s">
-        <v>20</v>
+        <v>377</v>
       </c>
     </row>
     <row r="578" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A578" s="1" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="B578" s="1">
-        <v>105</v>
+        <f>285+60</f>
+        <v>345</v>
       </c>
       <c r="C578" s="1" t="s">
-        <v>656</v>
+        <v>600</v>
       </c>
       <c r="D578" s="3" t="s">
         <v>35</v>
@@ -22182,69 +22198,69 @@
     </row>
     <row r="579" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A579" s="1" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="B579" s="1">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="C579" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D579" s="3" t="s">
-        <v>20</v>
+        <v>199</v>
       </c>
     </row>
     <row r="580" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A580" s="1" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="B580" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="C580" s="1" t="s">
-        <v>657</v>
+        <v>498</v>
       </c>
       <c r="D580" s="3" t="s">
-        <v>20</v>
+        <v>375</v>
       </c>
     </row>
     <row r="581" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A581" s="1" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B581" s="1">
         <v>40</v>
       </c>
       <c r="C581" s="1" t="s">
-        <v>485</v>
+        <v>653</v>
       </c>
       <c r="D581" s="3" t="s">
-        <v>377</v>
+        <v>20</v>
       </c>
     </row>
     <row r="582" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A582" s="1" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B582" s="1">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="C582" s="1" t="s">
-        <v>492</v>
+        <v>24</v>
       </c>
       <c r="D582" s="3" t="s">
-        <v>374</v>
+        <v>20</v>
       </c>
     </row>
     <row r="583" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A583" s="1" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B583" s="1">
-        <v>30</v>
+        <v>105</v>
       </c>
       <c r="C583" s="1" t="s">
-        <v>33</v>
+        <v>654</v>
       </c>
       <c r="D583" s="3" t="s">
         <v>35</v>
@@ -22252,30 +22268,30 @@
     </row>
     <row r="584" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A584" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B584" s="1">
         <v>75</v>
       </c>
       <c r="C584" s="1" t="s">
-        <v>24</v>
+        <v>356</v>
       </c>
       <c r="D584" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="585" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A585" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B585" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C585" s="1" t="s">
-        <v>23</v>
+        <v>655</v>
       </c>
       <c r="D585" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.45">
@@ -22283,13 +22299,13 @@
         <v>358</v>
       </c>
       <c r="B586" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C586" s="1" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="D586" s="3" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
     </row>
     <row r="587" spans="1:4" x14ac:dyDescent="0.45">
@@ -22297,13 +22313,13 @@
         <v>358</v>
       </c>
       <c r="B587" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C587" s="1" t="s">
-        <v>359</v>
+        <v>492</v>
       </c>
       <c r="D587" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="588" spans="1:4" x14ac:dyDescent="0.45">
@@ -22311,54 +22327,124 @@
         <v>358</v>
       </c>
       <c r="B588" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C588" s="1" t="s">
-        <v>501</v>
+        <v>33</v>
       </c>
       <c r="D588" s="3" t="s">
-        <v>376</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="589" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A589" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B589" s="1">
+        <v>75</v>
+      </c>
+      <c r="C589" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D589" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="590" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A590" s="1" t="s">
-        <v>382</v>
+        <v>358</v>
       </c>
       <c r="B590" s="1">
-        <f>SUM(B2:B588)</f>
-        <v>141913</v>
-      </c>
-      <c r="C590" s="1" t="str">
-        <f>"should be " &amp; 'New Gems (simplified per-rule)'!B820</f>
-        <v>should be 141913</v>
+        <v>50</v>
+      </c>
+      <c r="C590" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D590" s="3" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="591" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A591" s="1" t="s">
-        <v>17</v>
+        <v>358</v>
       </c>
       <c r="B591" s="1">
-        <v>20203</v>
+        <v>20</v>
+      </c>
+      <c r="C591" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="D591" s="3" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="592" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A592" s="1" t="s">
-        <v>603</v>
+        <v>358</v>
       </c>
       <c r="B592" s="1">
+        <v>50</v>
+      </c>
+      <c r="C592" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D592" s="3" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="593" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A593" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B593" s="1">
+        <v>20</v>
+      </c>
+      <c r="C593" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="D593" s="3" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="595" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A595" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B595" s="1">
+        <f>SUM(B2:B593)</f>
+        <v>141913</v>
+      </c>
+      <c r="C595" s="1" t="str">
+        <f>"should be " &amp; 'New Gems (simplified per-rule)'!B821</f>
+        <v>should be 141913</v>
+      </c>
+    </row>
+    <row r="596" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A596" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B596" s="1">
+        <v>20203</v>
+      </c>
+    </row>
+    <row r="597" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A597" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="B597" s="1">
         <v>16353</v>
       </c>
     </row>
-    <row r="593" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A593" s="1" t="s">
-        <v>604</v>
-      </c>
-      <c r="B593" s="1">
-        <f>B590-B591-B592</f>
+    <row r="598" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A598" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="B598" s="1">
+        <f>B595-B596-B597</f>
         <v>105357</v>
       </c>
-      <c r="C593" s="1" t="str">
-        <f>"should be " &amp; 'New Gems (simplified per-rule)'!B823</f>
+      <c r="C598" s="1" t="str">
+        <f>"should be " &amp; 'New Gems (simplified per-rule)'!B824</f>
         <v>should be 105357</v>
       </c>
     </row>
